--- a/inversiones_2026.xlsx
+++ b/inversiones_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\Documents\GitHub\inversiones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB47D6BB-FC82-4035-85E4-CEC99B33E526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2846AC-1F10-41F4-A288-6B69A69BD1C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro_Mensual" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="68">
   <si>
     <t>📈 SEGUIMIENTO DE INVERSIONES — S&amp;P 500</t>
   </si>
@@ -272,18 +272,22 @@
   </si>
   <si>
     <t>Diciembre</t>
+  </si>
+  <si>
+    <t>Spotify</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* &quot;-&quot;??\ [$€-C0A]_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -599,7 +603,7 @@
     <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -683,6 +687,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -714,14 +719,17 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
+    <dxf>
+      <numFmt numFmtId="168" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -740,6 +748,7 @@
         <charset val="1"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="167" formatCode="_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* &quot;-&quot;??\ [$€-C0A]_-;_-@_-"/>
@@ -1017,9 +1026,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Beneficios bolsa'!$E$3:$F$6</c:f>
+              <c:f>'Beneficios bolsa'!$E$3:$F$8</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="6"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>15-jul</c:v>
@@ -1032,6 +1041,12 @@
                   </c:pt>
                   <c:pt idx="3">
                     <c:v>29-jul</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>31-jul</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>20-ago</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1047,16 +1062,22 @@
                   <c:pt idx="3">
                     <c:v>Coca Cola</c:v>
                   </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Allianz</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Spotify</c:v>
+                  </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Beneficios bolsa'!$G$3:$G$6</c:f>
+              <c:f>'Beneficios bolsa'!$G$3:$G$8</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* "-"??\ [$€-C0A]_-;_-@_-</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1068,6 +1089,12 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>131</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>51</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1122,9 +1149,9 @@
           </c:marker>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Beneficios bolsa'!$E$3:$F$6</c:f>
+              <c:f>'Beneficios bolsa'!$E$3:$F$8</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="6"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>15-jul</c:v>
@@ -1137,6 +1164,12 @@
                   </c:pt>
                   <c:pt idx="3">
                     <c:v>29-jul</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>31-jul</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>20-ago</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1152,16 +1185,22 @@
                   <c:pt idx="3">
                     <c:v>Coca Cola</c:v>
                   </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Allianz</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Spotify</c:v>
+                  </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Beneficios bolsa'!$H$3:$H$6</c:f>
+              <c:f>'Beneficios bolsa'!$H$3:$H$8</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* "-"??\ [$€-C0A]_-;_-@_-</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1173,6 +1212,12 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>166.28</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>251.28</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>251.28</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1453,7 +1498,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Balance</c:v>
+                  <c:v> Balance </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1472,6 +1517,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1487,6 +1537,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1502,6 +1557,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1517,6 +1577,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1532,6 +1597,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1547,6 +1617,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1564,6 +1639,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -1581,6 +1661,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -1598,6 +1683,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -1615,6 +1705,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -1632,6 +1727,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
@@ -1649,6 +1749,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -1698,7 +1803,7 @@
             <c:numRef>
               <c:f>'Beneficios bolsa'!$P$3:$P$14</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1719,10 +1824,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>166.28</c:v>
+                  <c:v>200.28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1773,6 +1878,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1788,6 +1898,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1803,6 +1918,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1818,6 +1938,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1833,6 +1958,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1848,6 +1978,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1865,6 +2000,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000025-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -1882,6 +2022,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000027-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -1899,6 +2044,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000029-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -1916,6 +2066,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002B-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -1933,6 +2088,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002D-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
@@ -1950,6 +2110,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002F-1564-4888-8892-F5EE5EF4E767}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -2020,10 +2185,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1</c:v>
+                  <c:v>0.79703915950334292</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.20296084049665711</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -3317,14 +3482,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{43361EA0-38CE-405F-999E-E678479A76FE}" name="Tabla3" displayName="Tabla3" ref="B2:C11" totalsRowShown="0" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{43361EA0-38CE-405F-999E-E678479A76FE}" name="Tabla3" displayName="Tabla3" ref="B2:C11" totalsRowShown="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="B2:C11" xr:uid="{43361EA0-38CE-405F-999E-E678479A76FE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:C11">
     <sortCondition descending="1" ref="C3:C11"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5452176F-36B8-4CDD-9F33-5D70AA66A550}" name="Mercado" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{AA88D4F0-70F9-4823-81E5-D366BE0621A3}" name="Balance" dataDxfId="4" dataCellStyle="Moneda">
+    <tableColumn id="1" xr3:uid="{5452176F-36B8-4CDD-9F33-5D70AA66A550}" name="Mercado" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{AA88D4F0-70F9-4823-81E5-D366BE0621A3}" name="Balance" dataDxfId="5" dataCellStyle="Moneda">
       <calculatedColumnFormula>SUMIF(E:E,B3,G:G)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3333,13 +3498,13 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}" name="Tabla4" displayName="Tabla4" ref="E2:H6" totalsRowShown="0">
-  <autoFilter ref="E2:H6" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}" name="Tabla4" displayName="Tabla4" ref="E2:H8" totalsRowShown="0">
+  <autoFilter ref="E2:H8" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{D7244F53-013B-49D1-84D7-0E66C32F39B4}" name="Mercado"/>
-    <tableColumn id="2" xr3:uid="{28786B65-FA4E-4DA6-9569-A775903889EB}" name="Fecha venta" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00894C4B-3E6A-4755-9F14-59B8AD97246A}" name="Balance" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{2A5F1324-D18F-4866-A09B-AC0F8A8E977C}" name="Acumulado" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{28786B65-FA4E-4DA6-9569-A775903889EB}" name="Fecha venta" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00894C4B-3E6A-4755-9F14-59B8AD97246A}" name="Balance" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{2A5F1324-D18F-4866-A09B-AC0F8A8E977C}" name="Acumulado" dataDxfId="2">
       <calculatedColumnFormula>SUM($G$3:G3)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3352,11 +3517,11 @@
   <autoFilter ref="O2:Q14" xr:uid="{85052AB3-E623-41D6-B93A-D236D62ED596}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{21FC16B9-6E5E-4AAD-BCF0-C6A776FA39F3}" name="Mes"/>
-    <tableColumn id="2" xr3:uid="{37D9736B-4BBA-4113-BEB6-FB1048207595}" name="Balance">
-      <calculatedColumnFormula array="1">SUMPRODUCT(($F$3:$F$100&lt;&gt;"")*(TEXT($F$3:$F$100,"mmmm")=O3)*$G$3:$G$100)</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{37D9736B-4BBA-4113-BEB6-FB1048207595}" name="Balance" dataDxfId="0">
+      <calculatedColumnFormula array="1">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O3)*$G$3:$G$102)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5B181ADE-DC8F-4395-A0B1-0AC4441D7B3C}" name="Peso anual" dataDxfId="0" dataCellStyle="Porcentaje">
-      <calculatedColumnFormula>IFERROR(P3/SUM(P3:P14),0)</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{5B181ADE-DC8F-4395-A0B1-0AC4441D7B3C}" name="Peso anual" dataDxfId="1" dataCellStyle="Porcentaje">
+      <calculatedColumnFormula>IFERROR($P3/SUM($P$3:$P$14),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3554,30 +3719,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
+      <c r="A1" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -5583,32 +5748,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="D3" s="47" t="s">
+      <c r="B3" s="48"/>
+      <c r="D3" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="47"/>
+      <c r="E3" s="48"/>
       <c r="F3" s="16" t="s">
         <v>18</v>
       </c>
@@ -5624,10 +5789,10 @@
         <f>IFERROR(LOOKUP(2,1/(Registro_Mensual!G4:G63&lt;&gt;""),Registro_Mensual!G4:G63),"")</f>
         <v>406</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="48"/>
+      <c r="E4" s="49"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
@@ -5737,10 +5902,10 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="43"/>
+      <c r="B10" s="44"/>
       <c r="D10" s="17" t="s">
         <v>33</v>
       </c>
@@ -5777,64 +5942,64 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="44"/>
+      <c r="E12" s="45"/>
     </row>
     <row r="13" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
     </row>
     <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
     </row>
     <row r="15" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
     </row>
     <row r="16" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="41" t="s">
+      <c r="A16" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
     </row>
     <row r="17" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="42" t="s">
+      <c r="A17" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
     </row>
     <row r="18" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -5867,20 +6032,21 @@
     <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" style="32"/>
-    <col min="17" max="17" width="12.7109375" style="50" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" style="51"/>
+    <col min="17" max="17" width="12.7109375" style="39" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="E1" s="49" t="s">
+      <c r="C1" s="50"/>
+      <c r="E1" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" s="30" t="s">
@@ -5904,10 +6070,10 @@
       <c r="O2" t="s">
         <v>2</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="Q2" s="50" t="s">
+      <c r="Q2" s="39" t="s">
         <v>54</v>
       </c>
     </row>
@@ -5916,7 +6082,7 @@
         <v>42</v>
       </c>
       <c r="C3" s="27">
-        <f t="shared" ref="C3:C11" si="0">SUMIF(E:E,B3,G:G)</f>
+        <f>SUMIF(E:E,B3,G:G)</f>
         <v>131</v>
       </c>
       <c r="E3" t="s">
@@ -5935,12 +6101,12 @@
       <c r="O3" t="s">
         <v>55</v>
       </c>
-      <c r="P3" cm="1">
-        <f t="array" ref="P3">SUMPRODUCT(($F$3:$F$100&lt;&gt;"")*(TEXT($F$3:$F$100,"mmmm")=O3)*$G$3:$G$100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="50">
-        <f>IFERROR(P3/SUM(P3:P14),0)</f>
+      <c r="P3" s="51" cm="1">
+        <f t="array" ref="P3">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O3)*$G$3:$G$102)</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="39">
+        <f t="shared" ref="Q3:Q14" si="0">IFERROR($P3/SUM($P$3:$P$14),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5949,8 +6115,8 @@
         <v>44</v>
       </c>
       <c r="C4" s="27">
-        <f t="shared" si="0"/>
-        <v>19.399999999999999</v>
+        <f>SUMIF(E:E,B4,G:G)</f>
+        <v>53.4</v>
       </c>
       <c r="E4" t="s">
         <v>45</v>
@@ -5968,12 +6134,12 @@
       <c r="O4" t="s">
         <v>56</v>
       </c>
-      <c r="P4" cm="1">
-        <f t="array" ref="P4">SUMPRODUCT(($F$3:$F$100&lt;&gt;"")*(TEXT($F$3:$F$100,"mmmm")=O4)*$G$3:$G$100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="50">
-        <f t="shared" ref="Q4:Q14" si="1">IFERROR(P4/SUM(P4:P15),0)</f>
+      <c r="P4" s="51" cm="1">
+        <f t="array" ref="P4">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O4)*$G$3:$G$102)</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="39">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5982,7 +6148,7 @@
         <v>45</v>
       </c>
       <c r="C5" s="27">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E:E,B5,G:G)</f>
         <v>15.879999999999999</v>
       </c>
       <c r="E5" t="s">
@@ -6001,20 +6167,22 @@
       <c r="O5" t="s">
         <v>57</v>
       </c>
-      <c r="P5" cm="1">
-        <f t="array" ref="P5">SUMPRODUCT(($F$3:$F$100&lt;&gt;"")*(TEXT($F$3:$F$100,"mmmm")=O5)*$G$3:$G$100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="50">
-        <f t="shared" si="1"/>
+      <c r="P5" s="51" cm="1">
+        <f t="array" ref="P5">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O5)*$G$3:$G$102)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="39">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="26"/>
+      <c r="B6" s="26" t="s">
+        <v>67</v>
+      </c>
       <c r="C6" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUMIF(E:E,B6,G:G)</f>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
         <v>42</v>
@@ -6032,102 +6200,128 @@
       <c r="O6" t="s">
         <v>58</v>
       </c>
-      <c r="P6" cm="1">
-        <f t="array" ref="P6">SUMPRODUCT(($F$3:$F$100&lt;&gt;"")*(TEXT($F$3:$F$100,"mmmm")=O6)*$G$3:$G$100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="50">
-        <f t="shared" si="1"/>
+      <c r="P6" s="51" cm="1">
+        <f t="array" ref="P6">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O6)*$G$3:$G$102)</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="39">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="26"/>
       <c r="C7" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUMIF(E:E,B7,G:G)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="24">
+        <v>46234</v>
+      </c>
+      <c r="G7" s="32">
+        <v>34</v>
+      </c>
+      <c r="H7" s="32">
+        <f>SUM($G$3:G9)</f>
+        <v>251.28</v>
       </c>
       <c r="O7" t="s">
         <v>59</v>
       </c>
-      <c r="P7" cm="1">
-        <f t="array" ref="P7">SUMPRODUCT(($F$3:$F$100&lt;&gt;"")*(TEXT($F$3:$F$100,"mmmm")=O7)*$G$3:$G$100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="50">
-        <f t="shared" si="1"/>
+      <c r="P7" s="51" cm="1">
+        <f t="array" ref="P7">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O7)*$G$3:$G$102)</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="39">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="26"/>
       <c r="C8" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUMIF(E:E,B8,G:G)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="24">
+        <v>46254</v>
+      </c>
+      <c r="G8" s="32">
+        <v>51</v>
+      </c>
+      <c r="H8" s="32">
+        <f>SUM($G$3:G8)</f>
+        <v>251.28</v>
       </c>
       <c r="O8" t="s">
         <v>60</v>
       </c>
-      <c r="P8" cm="1">
-        <f t="array" ref="P8">SUMPRODUCT(($F$3:$F$100&lt;&gt;"")*(TEXT($F$3:$F$100,"mmmm")=O8)*$G$3:$G$100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="50">
-        <f t="shared" si="1"/>
+      <c r="P8" s="51" cm="1">
+        <f t="array" ref="P8">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O8)*$G$3:$G$102)</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="39">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="26"/>
       <c r="C9" s="27">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E:E,B9,G:G)</f>
         <v>0</v>
       </c>
       <c r="O9" t="s">
         <v>61</v>
       </c>
-      <c r="P9" cm="1">
-        <f t="array" ref="P9">SUMPRODUCT(($F$3:$F$100&lt;&gt;"")*(TEXT($F$3:$F$100,"mmmm")=O9)*$G$3:$G$100)</f>
-        <v>166.28</v>
-      </c>
-      <c r="Q9" s="50">
-        <f t="shared" si="1"/>
-        <v>1</v>
+      <c r="P9" s="51" cm="1">
+        <f t="array" ref="P9">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O9)*$G$3:$G$102)</f>
+        <v>200.28</v>
+      </c>
+      <c r="Q9" s="39">
+        <f t="shared" si="0"/>
+        <v>0.79703915950334292</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="26"/>
       <c r="C10" s="27">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E:E,B10,G:G)</f>
         <v>0</v>
       </c>
       <c r="O10" t="s">
         <v>62</v>
       </c>
-      <c r="P10" cm="1">
-        <f t="array" ref="P10">SUMPRODUCT(($F$3:$F$100&lt;&gt;"")*(TEXT($F$3:$F$100,"mmmm")=O10)*$G$3:$G$100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="50">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="P10" s="51" cm="1">
+        <f t="array" ref="P10">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O10)*$G$3:$G$102)</f>
+        <v>51</v>
+      </c>
+      <c r="Q10" s="39">
+        <f t="shared" si="0"/>
+        <v>0.20296084049665711</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="28"/>
       <c r="C11" s="29">
-        <f t="shared" si="0"/>
+        <f>SUMIF(E:E,B11,G:G)</f>
         <v>0</v>
       </c>
       <c r="O11" t="s">
         <v>63</v>
       </c>
-      <c r="P11" cm="1">
-        <f t="array" ref="P11">SUMPRODUCT(($F$3:$F$100&lt;&gt;"")*(TEXT($F$3:$F$100,"mmmm")=O11)*$G$3:$G$100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="50">
-        <f t="shared" si="1"/>
+      <c r="P11" s="51" cm="1">
+        <f t="array" ref="P11">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O11)*$G$3:$G$102)</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="39">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6137,17 +6331,17 @@
       </c>
       <c r="C12" s="38">
         <f>SUM(C3:C11)</f>
-        <v>166.28</v>
+        <v>251.28</v>
       </c>
       <c r="O12" t="s">
         <v>64</v>
       </c>
-      <c r="P12" cm="1">
-        <f t="array" ref="P12">SUMPRODUCT(($F$3:$F$100&lt;&gt;"")*(TEXT($F$3:$F$100,"mmmm")=O12)*$G$3:$G$100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="50">
-        <f t="shared" si="1"/>
+      <c r="P12" s="51" cm="1">
+        <f t="array" ref="P12">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O12)*$G$3:$G$102)</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="39">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6157,17 +6351,17 @@
       </c>
       <c r="C13" s="33">
         <f>C12*0.19*-1</f>
-        <v>-31.5932</v>
+        <v>-47.743200000000002</v>
       </c>
       <c r="O13" t="s">
         <v>65</v>
       </c>
-      <c r="P13" cm="1">
-        <f t="array" ref="P13">SUMPRODUCT(($F$3:$F$100&lt;&gt;"")*(TEXT($F$3:$F$100,"mmmm")=O13)*$G$3:$G$100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="50">
-        <f t="shared" si="1"/>
+      <c r="P13" s="51" cm="1">
+        <f t="array" ref="P13">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O13)*$G$3:$G$102)</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="39">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6177,17 +6371,17 @@
       </c>
       <c r="C14" s="36">
         <f>C12+C13</f>
-        <v>134.68680000000001</v>
+        <v>203.5368</v>
       </c>
       <c r="O14" t="s">
         <v>66</v>
       </c>
-      <c r="P14" cm="1">
-        <f t="array" ref="P14">SUMPRODUCT(($F$3:$F$100&lt;&gt;"")*(TEXT($F$3:$F$100,"mmmm")=O14)*$G$3:$G$100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="50">
-        <f t="shared" si="1"/>
+      <c r="P14" s="51" cm="1">
+        <f t="array" ref="P14">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O14)*$G$3:$G$102)</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="39">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>

--- a/inversiones_2026.xlsx
+++ b/inversiones_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\Documents\GitHub\inversiones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\Documents\GitHub\inversiones\inversiones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2846AC-1F10-41F4-A288-6B69A69BD1C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C5A905D-52F3-4E11-A456-7D759A66773F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro_Mensual" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Beneficios bolsa" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,9 +31,6 @@
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -61,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
   <si>
     <t>📈 SEGUIMIENTO DE INVERSIONES — S&amp;P 500</t>
   </si>
@@ -275,6 +273,9 @@
   </si>
   <si>
     <t>Spotify</t>
+  </si>
+  <si>
+    <t>Nvidia</t>
   </si>
 </sst>
 </file>
@@ -688,6 +689,7 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -719,7 +721,6 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -727,9 +728,6 @@
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <numFmt numFmtId="168" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -749,6 +747,9 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="167" formatCode="_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* &quot;-&quot;??\ [$€-C0A]_-;_-@_-"/>
@@ -1026,9 +1027,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Beneficios bolsa'!$E$3:$F$8</c:f>
+              <c:f>'Beneficios bolsa'!$E$3:$F$10</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="8"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>15-jul</c:v>
@@ -1047,6 +1048,12 @@
                   </c:pt>
                   <c:pt idx="5">
                     <c:v>20-ago</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>26-ago</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>27-ago</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1068,16 +1075,22 @@
                   <c:pt idx="5">
                     <c:v>Spotify</c:v>
                   </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Nvidia</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Nvidia</c:v>
+                  </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Beneficios bolsa'!$G$3:$G$8</c:f>
+              <c:f>'Beneficios bolsa'!$G$3:$G$10</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* "-"??\ [$€-C0A]_-;_-@_-</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1095,6 +1108,12 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>29.53</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>227.61</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1149,9 +1168,9 @@
           </c:marker>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Beneficios bolsa'!$E$3:$F$8</c:f>
+              <c:f>'Beneficios bolsa'!$E$3:$F$10</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="8"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>15-jul</c:v>
@@ -1170,6 +1189,12 @@
                   </c:pt>
                   <c:pt idx="5">
                     <c:v>20-ago</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>26-ago</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>27-ago</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1191,16 +1216,22 @@
                   <c:pt idx="5">
                     <c:v>Spotify</c:v>
                   </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Nvidia</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Nvidia</c:v>
+                  </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Beneficios bolsa'!$H$3:$H$8</c:f>
+              <c:f>'Beneficios bolsa'!$H$3:$H$10</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* "-"??\ [$€-C0A]_-;_-@_-</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1214,10 +1245,16 @@
                   <c:v>166.28</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>251.28</c:v>
+                  <c:v>200.28</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>251.28</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>280.81</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>508.42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1487,8 +1524,10 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:pieChart>
-        <c:varyColors val="1"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -1503,258 +1542,16 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="4"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="5"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="6"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="7"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="8"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="9"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="10"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000015-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="11"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000017-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>'Beneficios bolsa'!$O$3:$O$14</c:f>
@@ -1827,7 +1624,7 @@
                   <c:v>200.28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>51</c:v>
+                  <c:v>308.14</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1846,10 +1643,26 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6737-4125-AE2C-A6A201B90E4A}"/>
+              <c16:uniqueId val="{00000000-5008-4C6D-A5DF-F19A3C77E3E0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1267932496"/>
+        <c:axId val="1267929584"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -1864,258 +1677,18 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000019-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001B-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001D-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001F-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="4"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000021-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="5"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000023-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="6"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000025-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="7"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000027-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="8"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000029-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="9"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002B-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="10"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002D-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="11"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002F-1564-4888-8892-F5EE5EF4E767}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strRef>
               <c:f>'Beneficios bolsa'!$O$3:$O$14</c:f>
@@ -2185,10 +1758,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.79703915950334292</c:v>
+                  <c:v>0.39392628142087255</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.20296084049665711</c:v>
+                  <c:v>0.60607371857912751</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -2205,9 +1778,10 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-6737-4125-AE2C-A6A201B90E4A}"/>
+              <c16:uniqueId val="{00000001-5008-4C6D-A5DF-F19A3C77E3E0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2218,10 +1792,178 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1267942064"/>
+        <c:axId val="1267939568"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1267932496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1267929584"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1267929584"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1267932496"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1267939568"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1267942064"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1267942064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1267939568"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -2263,13 +2005,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -2886,7 +2621,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2943,7 +2678,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -2994,13 +2729,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -3011,19 +2739,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -3061,7 +2782,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -3104,23 +2825,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -3225,8 +2945,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3358,20 +3078,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -3444,23 +3163,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>281669</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>178973</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>312965</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>91167</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>706771</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>6403</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>557893</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>167367</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Gráfico 2">
+        <xdr:cNvPr id="4" name="Gráfico 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D76C996-5C27-483C-9405-D831259AB4CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22276D26-9FB6-49C5-B388-7DB35D315B81}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3498,8 +3217,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}" name="Tabla4" displayName="Tabla4" ref="E2:H8" totalsRowShown="0">
-  <autoFilter ref="E2:H8" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}" name="Tabla4" displayName="Tabla4" ref="E2:H10" totalsRowShown="0">
+  <autoFilter ref="E2:H10" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{D7244F53-013B-49D1-84D7-0E66C32F39B4}" name="Mercado"/>
     <tableColumn id="2" xr3:uid="{28786B65-FA4E-4DA6-9569-A775903889EB}" name="Fecha venta" dataDxfId="4"/>
@@ -3517,10 +3236,10 @@
   <autoFilter ref="O2:Q14" xr:uid="{85052AB3-E623-41D6-B93A-D236D62ED596}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{21FC16B9-6E5E-4AAD-BCF0-C6A776FA39F3}" name="Mes"/>
-    <tableColumn id="2" xr3:uid="{37D9736B-4BBA-4113-BEB6-FB1048207595}" name="Balance" dataDxfId="0">
-      <calculatedColumnFormula array="1">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O3)*$G$3:$G$102)</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{37D9736B-4BBA-4113-BEB6-FB1048207595}" name="Balance" dataDxfId="1">
+      <calculatedColumnFormula array="1">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O3)*$G$3:$G$104)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5B181ADE-DC8F-4395-A0B1-0AC4441D7B3C}" name="Peso anual" dataDxfId="1" dataCellStyle="Porcentaje">
+    <tableColumn id="3" xr3:uid="{5B181ADE-DC8F-4395-A0B1-0AC4441D7B3C}" name="Peso anual" dataDxfId="0" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IFERROR($P3/SUM($P$3:$P$14),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3719,30 +3438,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -5748,32 +5467,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="D3" s="48" t="s">
+      <c r="B3" s="49"/>
+      <c r="D3" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="48"/>
+      <c r="E3" s="49"/>
       <c r="F3" s="16" t="s">
         <v>18</v>
       </c>
@@ -5789,10 +5508,10 @@
         <f>IFERROR(LOOKUP(2,1/(Registro_Mensual!G4:G63&lt;&gt;""),Registro_Mensual!G4:G63),"")</f>
         <v>406</v>
       </c>
-      <c r="D4" s="49" t="s">
+      <c r="D4" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="49"/>
+      <c r="E4" s="50"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
@@ -5902,10 +5621,10 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="44"/>
+      <c r="B10" s="45"/>
       <c r="D10" s="17" t="s">
         <v>33</v>
       </c>
@@ -5942,64 +5661,64 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="45" t="s">
+      <c r="D12" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="45"/>
+      <c r="E12" s="46"/>
     </row>
     <row r="13" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
     </row>
     <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
     </row>
     <row r="15" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="43" t="s">
+      <c r="A15" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
     </row>
     <row r="16" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
     </row>
     <row r="17" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
     </row>
     <row r="18" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -6032,21 +5751,21 @@
     <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" style="32"/>
-    <col min="16" max="16" width="11.42578125" style="51"/>
+    <col min="16" max="16" width="11.42578125" style="40"/>
     <col min="17" max="17" width="12.7109375" style="39" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="E1" s="50" t="s">
+      <c r="C1" s="51"/>
+      <c r="E1" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" s="30" t="s">
@@ -6070,7 +5789,7 @@
       <c r="O2" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="51" t="s">
+      <c r="P2" s="40" t="s">
         <v>48</v>
       </c>
       <c r="Q2" s="39" t="s">
@@ -6101,8 +5820,8 @@
       <c r="O3" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="51" cm="1">
-        <f t="array" ref="P3">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O3)*$G$3:$G$102)</f>
+      <c r="P3" s="40" cm="1">
+        <f t="array" ref="P3">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O3)*$G$3:$G$104)</f>
         <v>0</v>
       </c>
       <c r="Q3" s="39">
@@ -6134,8 +5853,8 @@
       <c r="O4" t="s">
         <v>56</v>
       </c>
-      <c r="P4" s="51" cm="1">
-        <f t="array" ref="P4">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O4)*$G$3:$G$102)</f>
+      <c r="P4" s="40" cm="1">
+        <f t="array" ref="P4">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O4)*$G$3:$G$104)</f>
         <v>0</v>
       </c>
       <c r="Q4" s="39">
@@ -6167,8 +5886,8 @@
       <c r="O5" t="s">
         <v>57</v>
       </c>
-      <c r="P5" s="51" cm="1">
-        <f t="array" ref="P5">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O5)*$G$3:$G$102)</f>
+      <c r="P5" s="40" cm="1">
+        <f t="array" ref="P5">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O5)*$G$3:$G$104)</f>
         <v>0</v>
       </c>
       <c r="Q5" s="39">
@@ -6200,8 +5919,8 @@
       <c r="O6" t="s">
         <v>58</v>
       </c>
-      <c r="P6" s="51" cm="1">
-        <f t="array" ref="P6">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O6)*$G$3:$G$102)</f>
+      <c r="P6" s="40" cm="1">
+        <f t="array" ref="P6">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O6)*$G$3:$G$104)</f>
         <v>0</v>
       </c>
       <c r="Q6" s="39">
@@ -6210,10 +5929,12 @@
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="26"/>
+      <c r="B7" s="26" t="s">
+        <v>68</v>
+      </c>
       <c r="C7" s="27">
         <f>SUMIF(E:E,B7,G:G)</f>
-        <v>0</v>
+        <v>257.14</v>
       </c>
       <c r="E7" t="s">
         <v>44</v>
@@ -6225,14 +5946,14 @@
         <v>34</v>
       </c>
       <c r="H7" s="32">
-        <f>SUM($G$3:G9)</f>
-        <v>251.28</v>
+        <f>SUM($G$3:G7)</f>
+        <v>200.28</v>
       </c>
       <c r="O7" t="s">
         <v>59</v>
       </c>
-      <c r="P7" s="51" cm="1">
-        <f t="array" ref="P7">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O7)*$G$3:$G$102)</f>
+      <c r="P7" s="40" cm="1">
+        <f t="array" ref="P7">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O7)*$G$3:$G$104)</f>
         <v>0</v>
       </c>
       <c r="Q7" s="39">
@@ -6262,8 +5983,8 @@
       <c r="O8" t="s">
         <v>60</v>
       </c>
-      <c r="P8" s="51" cm="1">
-        <f t="array" ref="P8">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O8)*$G$3:$G$102)</f>
+      <c r="P8" s="40" cm="1">
+        <f t="array" ref="P8">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O8)*$G$3:$G$104)</f>
         <v>0</v>
       </c>
       <c r="Q8" s="39">
@@ -6277,16 +5998,29 @@
         <f>SUMIF(E:E,B9,G:G)</f>
         <v>0</v>
       </c>
+      <c r="E9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="24">
+        <v>46260</v>
+      </c>
+      <c r="G9" s="32">
+        <v>29.53</v>
+      </c>
+      <c r="H9" s="32">
+        <f>SUM($G$3:G9)</f>
+        <v>280.81</v>
+      </c>
       <c r="O9" t="s">
         <v>61</v>
       </c>
-      <c r="P9" s="51" cm="1">
-        <f t="array" ref="P9">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O9)*$G$3:$G$102)</f>
+      <c r="P9" s="40" cm="1">
+        <f t="array" ref="P9">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O9)*$G$3:$G$104)</f>
         <v>200.28</v>
       </c>
       <c r="Q9" s="39">
         <f t="shared" si="0"/>
-        <v>0.79703915950334292</v>
+        <v>0.39392628142087255</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
@@ -6295,16 +6029,29 @@
         <f>SUMIF(E:E,B10,G:G)</f>
         <v>0</v>
       </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="24">
+        <v>46261</v>
+      </c>
+      <c r="G10" s="32">
+        <v>227.61</v>
+      </c>
+      <c r="H10" s="32">
+        <f>SUM($G$3:G10)</f>
+        <v>508.42</v>
+      </c>
       <c r="O10" t="s">
         <v>62</v>
       </c>
-      <c r="P10" s="51" cm="1">
-        <f t="array" ref="P10">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O10)*$G$3:$G$102)</f>
-        <v>51</v>
+      <c r="P10" s="40" cm="1">
+        <f t="array" ref="P10">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O10)*$G$3:$G$104)</f>
+        <v>308.14</v>
       </c>
       <c r="Q10" s="39">
         <f t="shared" si="0"/>
-        <v>0.20296084049665711</v>
+        <v>0.60607371857912751</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
@@ -6316,8 +6063,8 @@
       <c r="O11" t="s">
         <v>63</v>
       </c>
-      <c r="P11" s="51" cm="1">
-        <f t="array" ref="P11">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O11)*$G$3:$G$102)</f>
+      <c r="P11" s="40" cm="1">
+        <f t="array" ref="P11">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O11)*$G$3:$G$104)</f>
         <v>0</v>
       </c>
       <c r="Q11" s="39">
@@ -6331,13 +6078,13 @@
       </c>
       <c r="C12" s="38">
         <f>SUM(C3:C11)</f>
-        <v>251.28</v>
+        <v>508.41999999999996</v>
       </c>
       <c r="O12" t="s">
         <v>64</v>
       </c>
-      <c r="P12" s="51" cm="1">
-        <f t="array" ref="P12">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O12)*$G$3:$G$102)</f>
+      <c r="P12" s="40" cm="1">
+        <f t="array" ref="P12">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O12)*$G$3:$G$104)</f>
         <v>0</v>
       </c>
       <c r="Q12" s="39">
@@ -6351,13 +6098,13 @@
       </c>
       <c r="C13" s="33">
         <f>C12*0.19*-1</f>
-        <v>-47.743200000000002</v>
+        <v>-96.599799999999988</v>
       </c>
       <c r="O13" t="s">
         <v>65</v>
       </c>
-      <c r="P13" s="51" cm="1">
-        <f t="array" ref="P13">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O13)*$G$3:$G$102)</f>
+      <c r="P13" s="40" cm="1">
+        <f t="array" ref="P13">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O13)*$G$3:$G$104)</f>
         <v>0</v>
       </c>
       <c r="Q13" s="39">
@@ -6371,13 +6118,13 @@
       </c>
       <c r="C14" s="36">
         <f>C12+C13</f>
-        <v>203.5368</v>
+        <v>411.8202</v>
       </c>
       <c r="O14" t="s">
         <v>66</v>
       </c>
-      <c r="P14" s="51" cm="1">
-        <f t="array" ref="P14">SUMPRODUCT(($F$3:$F$102&lt;&gt;"")*(TEXT($F$3:$F$102,"mmmm")=O14)*$G$3:$G$102)</f>
+      <c r="P14" s="40" cm="1">
+        <f t="array" ref="P14">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O14)*$G$3:$G$104)</f>
         <v>0</v>
       </c>
       <c r="Q14" s="39">

--- a/inversiones_2026.xlsx
+++ b/inversiones_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\Documents\GitHub\inversiones\inversiones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C5A905D-52F3-4E11-A456-7D759A66773F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BF6CC3-F268-480C-BA6F-AA2BED877C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,6 @@
     <sheet name="Beneficios bolsa" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -696,6 +695,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -707,15 +715,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1113,7 +1112,7 @@
                   <c:v>29.53</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>227.61</c:v>
+                  <c:v>337.61</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1254,7 +1253,7 @@
                   <c:v>280.81</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>508.42</c:v>
+                  <c:v>618.42000000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1624,7 +1623,7 @@
                   <c:v>200.28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>308.14</c:v>
+                  <c:v>418.14</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1758,10 +1757,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.39392628142087255</c:v>
+                  <c:v>0.3238575725235277</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.60607371857912751</c:v>
+                  <c:v>0.67614242747647235</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1959,6 +1958,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1267939568"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -3430,7 +3430,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -3656,31 +3656,37 @@
       <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="6"/>
+      <c r="B8" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C8" s="6">
+        <v>100</v>
+      </c>
       <c r="D8" s="7">
         <v>0</v>
       </c>
       <c r="E8" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="6"/>
+        <v>100</v>
+      </c>
+      <c r="F8" s="6">
+        <v>525</v>
+      </c>
       <c r="G8" s="9">
         <f>SUM($C$4:C8)</f>
-        <v>406</v>
-      </c>
-      <c r="H8" s="9" t="str">
+        <v>506</v>
+      </c>
+      <c r="H8" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I8" s="10" t="str">
+        <v>19</v>
+      </c>
+      <c r="I8" s="10">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3.7549407114624511E-2</v>
       </c>
       <c r="J8" s="9">
         <f>AVERAGE($E$4:E8)</f>
-        <v>79.400000000000006</v>
+        <v>99.4</v>
       </c>
       <c r="K8" s="11"/>
     </row>
@@ -3700,7 +3706,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="14">
         <f>SUM($C$4:C9)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H9" s="14" t="str">
         <f t="shared" si="1"/>
@@ -3712,7 +3718,7 @@
       </c>
       <c r="J9" s="14">
         <f>AVERAGE($E$4:E9)</f>
-        <v>66.166666666666671</v>
+        <v>82.833333333333329</v>
       </c>
       <c r="K9" s="11"/>
     </row>
@@ -3732,7 +3738,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="9">
         <f>SUM($C$4:C10)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H10" s="9" t="str">
         <f t="shared" si="1"/>
@@ -3744,7 +3750,7 @@
       </c>
       <c r="J10" s="9">
         <f>AVERAGE($E$4:E10)</f>
-        <v>56.714285714285715</v>
+        <v>71</v>
       </c>
       <c r="K10" s="11"/>
     </row>
@@ -3764,7 +3770,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="14">
         <f>SUM($C$4:C11)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H11" s="14" t="str">
         <f t="shared" si="1"/>
@@ -3776,7 +3782,7 @@
       </c>
       <c r="J11" s="14">
         <f>AVERAGE($E$4:E11)</f>
-        <v>49.625</v>
+        <v>62.125</v>
       </c>
       <c r="K11" s="11"/>
     </row>
@@ -3796,7 +3802,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="9">
         <f>SUM($C$4:C12)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H12" s="9" t="str">
         <f t="shared" si="1"/>
@@ -3808,7 +3814,7 @@
       </c>
       <c r="J12" s="9">
         <f>AVERAGE($E$4:E12)</f>
-        <v>44.111111111111114</v>
+        <v>55.222222222222221</v>
       </c>
       <c r="K12" s="11"/>
     </row>
@@ -3828,7 +3834,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="14">
         <f>SUM($C$4:C13)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H13" s="14" t="str">
         <f t="shared" si="1"/>
@@ -3840,7 +3846,7 @@
       </c>
       <c r="J13" s="14">
         <f>AVERAGE($E$4:E13)</f>
-        <v>39.700000000000003</v>
+        <v>49.7</v>
       </c>
       <c r="K13" s="11"/>
     </row>
@@ -3860,7 +3866,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="9">
         <f>SUM($C$4:C14)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H14" s="9" t="str">
         <f t="shared" si="1"/>
@@ -3872,7 +3878,7 @@
       </c>
       <c r="J14" s="9">
         <f>AVERAGE($E$4:E14)</f>
-        <v>36.090909090909093</v>
+        <v>45.18181818181818</v>
       </c>
       <c r="K14" s="11"/>
     </row>
@@ -3892,7 +3898,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="14">
         <f>SUM($C$4:C15)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H15" s="14" t="str">
         <f t="shared" si="1"/>
@@ -3904,7 +3910,7 @@
       </c>
       <c r="J15" s="14">
         <f>AVERAGE($E$4:E15)</f>
-        <v>33.083333333333336</v>
+        <v>41.416666666666664</v>
       </c>
       <c r="K15" s="11"/>
     </row>
@@ -3924,7 +3930,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="9">
         <f>SUM($C$4:C16)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H16" s="9" t="str">
         <f t="shared" si="1"/>
@@ -3936,7 +3942,7 @@
       </c>
       <c r="J16" s="9">
         <f>AVERAGE($E$4:E16)</f>
-        <v>30.53846153846154</v>
+        <v>38.230769230769234</v>
       </c>
       <c r="K16" s="11"/>
     </row>
@@ -3956,7 +3962,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="14">
         <f>SUM($C$4:C17)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H17" s="14" t="str">
         <f t="shared" si="1"/>
@@ -3968,7 +3974,7 @@
       </c>
       <c r="J17" s="14">
         <f>AVERAGE($E$4:E17)</f>
-        <v>28.357142857142858</v>
+        <v>35.5</v>
       </c>
       <c r="K17" s="11"/>
     </row>
@@ -3988,7 +3994,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="9">
         <f>SUM($C$4:C18)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H18" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4000,7 +4006,7 @@
       </c>
       <c r="J18" s="9">
         <f>AVERAGE($E$4:E18)</f>
-        <v>26.466666666666665</v>
+        <v>33.133333333333333</v>
       </c>
       <c r="K18" s="11"/>
     </row>
@@ -4020,7 +4026,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="14">
         <f>SUM($C$4:C19)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H19" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4032,7 +4038,7 @@
       </c>
       <c r="J19" s="14">
         <f>AVERAGE($E$4:E19)</f>
-        <v>24.8125</v>
+        <v>31.0625</v>
       </c>
       <c r="K19" s="11"/>
     </row>
@@ -4052,7 +4058,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="9">
         <f>SUM($C$4:C20)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H20" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4064,7 +4070,7 @@
       </c>
       <c r="J20" s="9">
         <f>AVERAGE($E$4:E20)</f>
-        <v>23.352941176470587</v>
+        <v>29.235294117647058</v>
       </c>
       <c r="K20" s="11"/>
     </row>
@@ -4084,7 +4090,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="14">
         <f>SUM($C$4:C21)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H21" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4096,7 +4102,7 @@
       </c>
       <c r="J21" s="14">
         <f>AVERAGE($E$4:E21)</f>
-        <v>22.055555555555557</v>
+        <v>27.611111111111111</v>
       </c>
       <c r="K21" s="11"/>
     </row>
@@ -4116,7 +4122,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="9">
         <f>SUM($C$4:C22)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H22" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4128,7 +4134,7 @@
       </c>
       <c r="J22" s="9">
         <f>AVERAGE($E$4:E22)</f>
-        <v>20.894736842105264</v>
+        <v>26.157894736842106</v>
       </c>
       <c r="K22" s="11"/>
     </row>
@@ -4148,7 +4154,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="14">
         <f>SUM($C$4:C23)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H23" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4160,7 +4166,7 @@
       </c>
       <c r="J23" s="14">
         <f>AVERAGE($E$4:E23)</f>
-        <v>19.850000000000001</v>
+        <v>24.85</v>
       </c>
       <c r="K23" s="11"/>
     </row>
@@ -4180,7 +4186,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="9">
         <f>SUM($C$4:C24)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H24" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4192,7 +4198,7 @@
       </c>
       <c r="J24" s="9">
         <f>AVERAGE($E$4:E24)</f>
-        <v>18.904761904761905</v>
+        <v>23.666666666666668</v>
       </c>
       <c r="K24" s="11"/>
     </row>
@@ -4212,7 +4218,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="14">
         <f>SUM($C$4:C25)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H25" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4224,7 +4230,7 @@
       </c>
       <c r="J25" s="14">
         <f>AVERAGE($E$4:E25)</f>
-        <v>18.045454545454547</v>
+        <v>22.59090909090909</v>
       </c>
       <c r="K25" s="11"/>
     </row>
@@ -4244,7 +4250,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="9">
         <f>SUM($C$4:C26)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H26" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4256,7 +4262,7 @@
       </c>
       <c r="J26" s="9">
         <f>AVERAGE($E$4:E26)</f>
-        <v>17.260869565217391</v>
+        <v>21.608695652173914</v>
       </c>
       <c r="K26" s="11"/>
     </row>
@@ -4276,7 +4282,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="14">
         <f>SUM($C$4:C27)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H27" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4288,7 +4294,7 @@
       </c>
       <c r="J27" s="14">
         <f>AVERAGE($E$4:E27)</f>
-        <v>16.541666666666668</v>
+        <v>20.708333333333332</v>
       </c>
       <c r="K27" s="11"/>
     </row>
@@ -4308,7 +4314,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="9">
         <f>SUM($C$4:C28)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H28" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4320,7 +4326,7 @@
       </c>
       <c r="J28" s="9">
         <f>AVERAGE($E$4:E28)</f>
-        <v>15.88</v>
+        <v>19.88</v>
       </c>
       <c r="K28" s="11"/>
     </row>
@@ -4340,7 +4346,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="14">
         <f>SUM($C$4:C29)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H29" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4352,7 +4358,7 @@
       </c>
       <c r="J29" s="14">
         <f>AVERAGE($E$4:E29)</f>
-        <v>15.26923076923077</v>
+        <v>19.115384615384617</v>
       </c>
       <c r="K29" s="11"/>
     </row>
@@ -4372,7 +4378,7 @@
       <c r="F30" s="6"/>
       <c r="G30" s="9">
         <f>SUM($C$4:C30)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H30" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4384,7 +4390,7 @@
       </c>
       <c r="J30" s="9">
         <f>AVERAGE($E$4:E30)</f>
-        <v>14.703703703703704</v>
+        <v>18.407407407407408</v>
       </c>
       <c r="K30" s="11"/>
     </row>
@@ -4404,7 +4410,7 @@
       <c r="F31" s="6"/>
       <c r="G31" s="14">
         <f>SUM($C$4:C31)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H31" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4416,7 +4422,7 @@
       </c>
       <c r="J31" s="14">
         <f>AVERAGE($E$4:E31)</f>
-        <v>14.178571428571429</v>
+        <v>17.75</v>
       </c>
       <c r="K31" s="11"/>
     </row>
@@ -4436,7 +4442,7 @@
       <c r="F32" s="6"/>
       <c r="G32" s="9">
         <f>SUM($C$4:C32)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H32" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4448,7 +4454,7 @@
       </c>
       <c r="J32" s="9">
         <f>AVERAGE($E$4:E32)</f>
-        <v>13.689655172413794</v>
+        <v>17.137931034482758</v>
       </c>
       <c r="K32" s="11"/>
     </row>
@@ -4468,7 +4474,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="14">
         <f>SUM($C$4:C33)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H33" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4480,7 +4486,7 @@
       </c>
       <c r="J33" s="14">
         <f>AVERAGE($E$4:E33)</f>
-        <v>13.233333333333333</v>
+        <v>16.566666666666666</v>
       </c>
       <c r="K33" s="11"/>
     </row>
@@ -4500,7 +4506,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="9">
         <f>SUM($C$4:C34)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H34" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4512,7 +4518,7 @@
       </c>
       <c r="J34" s="9">
         <f>AVERAGE($E$4:E34)</f>
-        <v>12.806451612903226</v>
+        <v>16.032258064516128</v>
       </c>
       <c r="K34" s="11"/>
     </row>
@@ -4532,7 +4538,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="14">
         <f>SUM($C$4:C35)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H35" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4544,7 +4550,7 @@
       </c>
       <c r="J35" s="14">
         <f>AVERAGE($E$4:E35)</f>
-        <v>12.40625</v>
+        <v>15.53125</v>
       </c>
       <c r="K35" s="11"/>
     </row>
@@ -4564,7 +4570,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="9">
         <f>SUM($C$4:C36)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H36" s="9" t="str">
         <f t="shared" ref="H36:H63" si="4">IF(F36="","",F36-G36)</f>
@@ -4576,7 +4582,7 @@
       </c>
       <c r="J36" s="9">
         <f>AVERAGE($E$4:E36)</f>
-        <v>12.030303030303031</v>
+        <v>15.060606060606061</v>
       </c>
       <c r="K36" s="11"/>
     </row>
@@ -4596,7 +4602,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="14">
         <f>SUM($C$4:C37)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H37" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4608,7 +4614,7 @@
       </c>
       <c r="J37" s="14">
         <f>AVERAGE($E$4:E37)</f>
-        <v>11.676470588235293</v>
+        <v>14.617647058823529</v>
       </c>
       <c r="K37" s="11"/>
     </row>
@@ -4628,7 +4634,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="9">
         <f>SUM($C$4:C38)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H38" s="9" t="str">
         <f t="shared" si="4"/>
@@ -4640,7 +4646,7 @@
       </c>
       <c r="J38" s="9">
         <f>AVERAGE($E$4:E38)</f>
-        <v>11.342857142857143</v>
+        <v>14.2</v>
       </c>
       <c r="K38" s="11"/>
     </row>
@@ -4660,7 +4666,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="14">
         <f>SUM($C$4:C39)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H39" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4672,7 +4678,7 @@
       </c>
       <c r="J39" s="14">
         <f>AVERAGE($E$4:E39)</f>
-        <v>11.027777777777779</v>
+        <v>13.805555555555555</v>
       </c>
       <c r="K39" s="11"/>
     </row>
@@ -4692,7 +4698,7 @@
       <c r="F40" s="6"/>
       <c r="G40" s="9">
         <f>SUM($C$4:C40)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H40" s="9" t="str">
         <f t="shared" si="4"/>
@@ -4704,7 +4710,7 @@
       </c>
       <c r="J40" s="9">
         <f>AVERAGE($E$4:E40)</f>
-        <v>10.72972972972973</v>
+        <v>13.432432432432432</v>
       </c>
       <c r="K40" s="11"/>
     </row>
@@ -4724,7 +4730,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="14">
         <f>SUM($C$4:C41)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H41" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4736,7 +4742,7 @@
       </c>
       <c r="J41" s="14">
         <f>AVERAGE($E$4:E41)</f>
-        <v>10.447368421052632</v>
+        <v>13.078947368421053</v>
       </c>
       <c r="K41" s="11"/>
     </row>
@@ -4756,7 +4762,7 @@
       <c r="F42" s="6"/>
       <c r="G42" s="9">
         <f>SUM($C$4:C42)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H42" s="9" t="str">
         <f t="shared" si="4"/>
@@ -4768,7 +4774,7 @@
       </c>
       <c r="J42" s="9">
         <f>AVERAGE($E$4:E42)</f>
-        <v>10.179487179487179</v>
+        <v>12.743589743589743</v>
       </c>
       <c r="K42" s="11"/>
     </row>
@@ -4788,7 +4794,7 @@
       <c r="F43" s="6"/>
       <c r="G43" s="14">
         <f>SUM($C$4:C43)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H43" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4800,7 +4806,7 @@
       </c>
       <c r="J43" s="14">
         <f>AVERAGE($E$4:E43)</f>
-        <v>9.9250000000000007</v>
+        <v>12.425000000000001</v>
       </c>
       <c r="K43" s="11"/>
     </row>
@@ -4820,7 +4826,7 @@
       <c r="F44" s="6"/>
       <c r="G44" s="9">
         <f>SUM($C$4:C44)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H44" s="9" t="str">
         <f t="shared" si="4"/>
@@ -4832,7 +4838,7 @@
       </c>
       <c r="J44" s="9">
         <f>AVERAGE($E$4:E44)</f>
-        <v>9.6829268292682933</v>
+        <v>12.121951219512194</v>
       </c>
       <c r="K44" s="11"/>
     </row>
@@ -4852,7 +4858,7 @@
       <c r="F45" s="6"/>
       <c r="G45" s="14">
         <f>SUM($C$4:C45)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H45" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4864,7 +4870,7 @@
       </c>
       <c r="J45" s="14">
         <f>AVERAGE($E$4:E45)</f>
-        <v>9.4523809523809526</v>
+        <v>11.833333333333334</v>
       </c>
       <c r="K45" s="11"/>
     </row>
@@ -4884,7 +4890,7 @@
       <c r="F46" s="6"/>
       <c r="G46" s="9">
         <f>SUM($C$4:C46)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H46" s="9" t="str">
         <f t="shared" si="4"/>
@@ -4896,7 +4902,7 @@
       </c>
       <c r="J46" s="9">
         <f>AVERAGE($E$4:E46)</f>
-        <v>9.2325581395348841</v>
+        <v>11.55813953488372</v>
       </c>
       <c r="K46" s="11"/>
     </row>
@@ -4916,7 +4922,7 @@
       <c r="F47" s="6"/>
       <c r="G47" s="14">
         <f>SUM($C$4:C47)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H47" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4928,7 +4934,7 @@
       </c>
       <c r="J47" s="14">
         <f>AVERAGE($E$4:E47)</f>
-        <v>9.0227272727272734</v>
+        <v>11.295454545454545</v>
       </c>
       <c r="K47" s="11"/>
     </row>
@@ -4948,7 +4954,7 @@
       <c r="F48" s="6"/>
       <c r="G48" s="9">
         <f>SUM($C$4:C48)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H48" s="9" t="str">
         <f t="shared" si="4"/>
@@ -4960,7 +4966,7 @@
       </c>
       <c r="J48" s="9">
         <f>AVERAGE($E$4:E48)</f>
-        <v>8.8222222222222229</v>
+        <v>11.044444444444444</v>
       </c>
       <c r="K48" s="11"/>
     </row>
@@ -4980,7 +4986,7 @@
       <c r="F49" s="6"/>
       <c r="G49" s="14">
         <f>SUM($C$4:C49)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H49" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4992,7 +4998,7 @@
       </c>
       <c r="J49" s="14">
         <f>AVERAGE($E$4:E49)</f>
-        <v>8.6304347826086953</v>
+        <v>10.804347826086957</v>
       </c>
       <c r="K49" s="11"/>
     </row>
@@ -5012,7 +5018,7 @@
       <c r="F50" s="6"/>
       <c r="G50" s="9">
         <f>SUM($C$4:C50)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H50" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5024,7 +5030,7 @@
       </c>
       <c r="J50" s="9">
         <f>AVERAGE($E$4:E50)</f>
-        <v>8.4468085106382986</v>
+        <v>10.574468085106384</v>
       </c>
       <c r="K50" s="11"/>
     </row>
@@ -5044,7 +5050,7 @@
       <c r="F51" s="6"/>
       <c r="G51" s="14">
         <f>SUM($C$4:C51)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H51" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5056,7 +5062,7 @@
       </c>
       <c r="J51" s="14">
         <f>AVERAGE($E$4:E51)</f>
-        <v>8.2708333333333339</v>
+        <v>10.354166666666666</v>
       </c>
       <c r="K51" s="11"/>
     </row>
@@ -5076,7 +5082,7 @@
       <c r="F52" s="6"/>
       <c r="G52" s="9">
         <f>SUM($C$4:C52)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H52" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5088,7 +5094,7 @@
       </c>
       <c r="J52" s="9">
         <f>AVERAGE($E$4:E52)</f>
-        <v>8.1020408163265305</v>
+        <v>10.142857142857142</v>
       </c>
       <c r="K52" s="11"/>
     </row>
@@ -5108,7 +5114,7 @@
       <c r="F53" s="6"/>
       <c r="G53" s="14">
         <f>SUM($C$4:C53)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H53" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5120,7 +5126,7 @@
       </c>
       <c r="J53" s="14">
         <f>AVERAGE($E$4:E53)</f>
-        <v>7.94</v>
+        <v>9.94</v>
       </c>
       <c r="K53" s="11"/>
     </row>
@@ -5140,7 +5146,7 @@
       <c r="F54" s="6"/>
       <c r="G54" s="9">
         <f>SUM($C$4:C54)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H54" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5152,7 +5158,7 @@
       </c>
       <c r="J54" s="9">
         <f>AVERAGE($E$4:E54)</f>
-        <v>7.784313725490196</v>
+        <v>9.7450980392156854</v>
       </c>
       <c r="K54" s="11"/>
     </row>
@@ -5172,7 +5178,7 @@
       <c r="F55" s="6"/>
       <c r="G55" s="14">
         <f>SUM($C$4:C55)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H55" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5184,7 +5190,7 @@
       </c>
       <c r="J55" s="14">
         <f>AVERAGE($E$4:E55)</f>
-        <v>7.634615384615385</v>
+        <v>9.5576923076923084</v>
       </c>
       <c r="K55" s="11"/>
     </row>
@@ -5204,7 +5210,7 @@
       <c r="F56" s="6"/>
       <c r="G56" s="9">
         <f>SUM($C$4:C56)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H56" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5216,7 +5222,7 @@
       </c>
       <c r="J56" s="9">
         <f>AVERAGE($E$4:E56)</f>
-        <v>7.4905660377358494</v>
+        <v>9.3773584905660385</v>
       </c>
       <c r="K56" s="11"/>
     </row>
@@ -5236,7 +5242,7 @@
       <c r="F57" s="6"/>
       <c r="G57" s="14">
         <f>SUM($C$4:C57)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H57" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5248,7 +5254,7 @@
       </c>
       <c r="J57" s="14">
         <f>AVERAGE($E$4:E57)</f>
-        <v>7.3518518518518521</v>
+        <v>9.2037037037037042</v>
       </c>
       <c r="K57" s="11"/>
     </row>
@@ -5268,7 +5274,7 @@
       <c r="F58" s="6"/>
       <c r="G58" s="9">
         <f>SUM($C$4:C58)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H58" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5280,7 +5286,7 @@
       </c>
       <c r="J58" s="9">
         <f>AVERAGE($E$4:E58)</f>
-        <v>7.2181818181818178</v>
+        <v>9.036363636363637</v>
       </c>
       <c r="K58" s="11"/>
     </row>
@@ -5300,7 +5306,7 @@
       <c r="F59" s="6"/>
       <c r="G59" s="14">
         <f>SUM($C$4:C59)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H59" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5312,7 +5318,7 @@
       </c>
       <c r="J59" s="14">
         <f>AVERAGE($E$4:E59)</f>
-        <v>7.0892857142857144</v>
+        <v>8.875</v>
       </c>
       <c r="K59" s="11"/>
     </row>
@@ -5332,7 +5338,7 @@
       <c r="F60" s="6"/>
       <c r="G60" s="9">
         <f>SUM($C$4:C60)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H60" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5344,7 +5350,7 @@
       </c>
       <c r="J60" s="9">
         <f>AVERAGE($E$4:E60)</f>
-        <v>6.9649122807017543</v>
+        <v>8.7192982456140342</v>
       </c>
       <c r="K60" s="11"/>
     </row>
@@ -5364,7 +5370,7 @@
       <c r="F61" s="6"/>
       <c r="G61" s="14">
         <f>SUM($C$4:C61)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H61" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5376,7 +5382,7 @@
       </c>
       <c r="J61" s="14">
         <f>AVERAGE($E$4:E61)</f>
-        <v>6.8448275862068968</v>
+        <v>8.568965517241379</v>
       </c>
       <c r="K61" s="11"/>
     </row>
@@ -5396,7 +5402,7 @@
       <c r="F62" s="6"/>
       <c r="G62" s="9">
         <f>SUM($C$4:C62)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H62" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5408,7 +5414,7 @@
       </c>
       <c r="J62" s="9">
         <f>AVERAGE($E$4:E62)</f>
-        <v>6.7288135593220337</v>
+        <v>8.4237288135593218</v>
       </c>
       <c r="K62" s="11"/>
     </row>
@@ -5428,7 +5434,7 @@
       <c r="F63" s="6"/>
       <c r="G63" s="14">
         <f>SUM($C$4:C63)</f>
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="H63" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5440,7 +5446,7 @@
       </c>
       <c r="J63" s="14">
         <f>AVERAGE($E$4:E63)</f>
-        <v>6.6166666666666663</v>
+        <v>8.2833333333333332</v>
       </c>
       <c r="K63" s="11"/>
     </row>
@@ -5467,13 +5473,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
@@ -5485,14 +5491,14 @@
       <c r="E2" s="42"/>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="D3" s="49" t="s">
+      <c r="B3" s="44"/>
+      <c r="D3" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="49"/>
+      <c r="E3" s="44"/>
       <c r="F3" s="16" t="s">
         <v>18</v>
       </c>
@@ -5506,12 +5512,12 @@
       </c>
       <c r="B4" s="18">
         <f>IFERROR(LOOKUP(2,1/(Registro_Mensual!G4:G63&lt;&gt;""),Registro_Mensual!G4:G63),"")</f>
-        <v>406</v>
-      </c>
-      <c r="D4" s="50" t="s">
+        <v>506</v>
+      </c>
+      <c r="D4" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="50"/>
+      <c r="E4" s="45"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
@@ -5519,14 +5525,14 @@
       </c>
       <c r="B5" s="18">
         <f ca="1">OFFSET(Registro_Mensual!F3,COUNTA(Registro_Mensual!F4:F63),0)</f>
-        <v>420</v>
+        <v>525</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="18">
         <f>B8</f>
-        <v>99.25</v>
+        <v>99.4</v>
       </c>
       <c r="F5" s="19"/>
       <c r="G5" s="19"/>
@@ -5537,13 +5543,13 @@
       </c>
       <c r="B6" s="18">
         <f ca="1">IFERROR(B5-B4,"")</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="20">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F6" s="19"/>
       <c r="G6" s="19"/>
@@ -5554,22 +5560,22 @@
       </c>
       <c r="B7" s="21">
         <f ca="1">IFERROR(B5/B4-1,"")</f>
-        <v>3.4482758620689724E-2</v>
+        <v>3.7549407114624511E-2</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="18">
         <f>E5*((1+E6/12)^60-1)/(E6/12)</f>
-        <v>7292.5779823401608</v>
+        <v>7116.3344238223854</v>
       </c>
       <c r="F7" s="23">
         <f>E5*60</f>
-        <v>5955</v>
+        <v>5964</v>
       </c>
       <c r="G7" s="23">
         <f>E7-F7</f>
-        <v>1337.5779823401608</v>
+        <v>1152.3344238223854</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5578,22 +5584,22 @@
       </c>
       <c r="B8" s="18">
         <f>IFERROR(AVERAGEIF(Registro_Mensual!C4:C63,"&gt;0",Registro_Mensual!E4:E63),"")</f>
-        <v>99.25</v>
+        <v>99.4</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E8" s="18">
         <f>E5*((1+E6/12)^120-1)/(E6/12)</f>
-        <v>18157.393991784433</v>
+        <v>17204.629858893561</v>
       </c>
       <c r="F8" s="23">
         <f>E5*120</f>
-        <v>11910</v>
+        <v>11928</v>
       </c>
       <c r="G8" s="23">
         <f>E8-F8</f>
-        <v>6247.3939917844327</v>
+        <v>5276.6298588935606</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5602,43 +5608,43 @@
       </c>
       <c r="B9" s="22">
         <f>COUNTIF(Registro_Mensual!C4:C63,"&gt;0")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="18">
         <f>E5*((1+E6/12)^240-1)/(E6/12)</f>
-        <v>58460.276250429619</v>
+        <v>51780.109986656382</v>
       </c>
       <c r="F9" s="23">
         <f>E5*240</f>
-        <v>23820</v>
+        <v>23856</v>
       </c>
       <c r="G9" s="23">
         <f>E9-F9</f>
-        <v>34640.276250429619</v>
+        <v>27924.109986656382</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="45"/>
+      <c r="B10" s="48"/>
       <c r="D10" s="17" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="18">
         <f>E5*((1+E6/12)^360-1)/(E6/12)</f>
-        <v>147918.17527983681</v>
+        <v>121265.11698012863</v>
       </c>
       <c r="F10" s="23">
         <f>E5*360</f>
-        <v>35730</v>
+        <v>35784</v>
       </c>
       <c r="G10" s="23">
         <f>E10-F10</f>
-        <v>112188.17527983681</v>
+        <v>85481.116980128631</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5649,84 +5655,79 @@
       </c>
       <c r="E11" s="18">
         <f>E5*((1+E6/12)^480-1)/(E6/12)</f>
-        <v>346482.52726334758</v>
+        <v>260906.45179433568</v>
       </c>
       <c r="F11" s="23">
         <f>E5*480</f>
-        <v>47640</v>
+        <v>47712</v>
       </c>
       <c r="G11" s="23">
         <f>E11-F11</f>
-        <v>298842.52726334758</v>
+        <v>213194.45179433568</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="46"/>
+      <c r="E12" s="49"/>
     </row>
     <row r="13" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
     </row>
     <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
     </row>
     <row r="15" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
     </row>
     <row r="16" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
     </row>
     <row r="17" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
     </row>
     <row r="18" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
@@ -5735,6 +5736,11 @@
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5834,7 +5840,7 @@
         <v>44</v>
       </c>
       <c r="C4" s="27">
-        <f>SUMIF(E:E,B4,G:G)</f>
+        <f t="shared" ref="C4:C11" si="1">SUMIF(E:E,B4,G:G)</f>
         <v>53.4</v>
       </c>
       <c r="E4" t="s">
@@ -5867,7 +5873,7 @@
         <v>45</v>
       </c>
       <c r="C5" s="27">
-        <f>SUMIF(E:E,B5,G:G)</f>
+        <f t="shared" si="1"/>
         <v>15.879999999999999</v>
       </c>
       <c r="E5" t="s">
@@ -5900,7 +5906,7 @@
         <v>67</v>
       </c>
       <c r="C6" s="27">
-        <f>SUMIF(E:E,B6,G:G)</f>
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="E6" t="s">
@@ -5933,8 +5939,8 @@
         <v>68</v>
       </c>
       <c r="C7" s="27">
-        <f>SUMIF(E:E,B7,G:G)</f>
-        <v>257.14</v>
+        <f t="shared" si="1"/>
+        <v>367.14</v>
       </c>
       <c r="E7" t="s">
         <v>44</v>
@@ -5964,7 +5970,7 @@
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="26"/>
       <c r="C8" s="27">
-        <f>SUMIF(E:E,B8,G:G)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E8" t="s">
@@ -5995,7 +6001,7 @@
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="26"/>
       <c r="C9" s="27">
-        <f>SUMIF(E:E,B9,G:G)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E9" t="s">
@@ -6020,13 +6026,13 @@
       </c>
       <c r="Q9" s="39">
         <f t="shared" si="0"/>
-        <v>0.39392628142087255</v>
+        <v>0.3238575725235277</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="26"/>
       <c r="C10" s="27">
-        <f>SUMIF(E:E,B10,G:G)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E10" t="s">
@@ -6036,28 +6042,28 @@
         <v>46261</v>
       </c>
       <c r="G10" s="32">
-        <v>227.61</v>
+        <v>337.61</v>
       </c>
       <c r="H10" s="32">
         <f>SUM($G$3:G10)</f>
-        <v>508.42</v>
+        <v>618.42000000000007</v>
       </c>
       <c r="O10" t="s">
         <v>62</v>
       </c>
       <c r="P10" s="40" cm="1">
         <f t="array" ref="P10">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O10)*$G$3:$G$104)</f>
-        <v>308.14</v>
+        <v>418.14</v>
       </c>
       <c r="Q10" s="39">
         <f t="shared" si="0"/>
-        <v>0.60607371857912751</v>
+        <v>0.67614242747647235</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="28"/>
       <c r="C11" s="29">
-        <f>SUMIF(E:E,B11,G:G)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O11" t="s">
@@ -6078,7 +6084,7 @@
       </c>
       <c r="C12" s="38">
         <f>SUM(C3:C11)</f>
-        <v>508.41999999999996</v>
+        <v>618.41999999999996</v>
       </c>
       <c r="O12" t="s">
         <v>64</v>
@@ -6098,7 +6104,7 @@
       </c>
       <c r="C13" s="33">
         <f>C12*0.19*-1</f>
-        <v>-96.599799999999988</v>
+        <v>-117.49979999999999</v>
       </c>
       <c r="O13" t="s">
         <v>65</v>
@@ -6118,7 +6124,7 @@
       </c>
       <c r="C14" s="36">
         <f>C12+C13</f>
-        <v>411.8202</v>
+        <v>500.92019999999997</v>
       </c>
       <c r="O14" t="s">
         <v>66</v>

--- a/inversiones_2026.xlsx
+++ b/inversiones_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\Documents\GitHub\inversiones\inversiones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BF6CC3-F268-480C-BA6F-AA2BED877C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E6BCF5-8D27-41F1-85CC-C29606E5E96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -695,15 +695,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -715,6 +706,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1112,7 +1112,7 @@
                   <c:v>29.53</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>337.61</c:v>
+                  <c:v>377.61</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1253,7 +1253,7 @@
                   <c:v>280.81</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>618.42000000000007</c:v>
+                  <c:v>658.42000000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1623,7 +1623,7 @@
                   <c:v>200.28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>418.14</c:v>
+                  <c:v>458.14</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1757,10 +1757,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3238575725235277</c:v>
+                  <c:v>0.30418274049998484</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.67614242747647235</c:v>
+                  <c:v>0.69581725950001516</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -5473,13 +5473,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
@@ -5491,14 +5491,14 @@
       <c r="E2" s="42"/>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="D3" s="44" t="s">
+      <c r="B3" s="49"/>
+      <c r="D3" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="44"/>
+      <c r="E3" s="49"/>
       <c r="F3" s="16" t="s">
         <v>18</v>
       </c>
@@ -5514,10 +5514,10 @@
         <f>IFERROR(LOOKUP(2,1/(Registro_Mensual!G4:G63&lt;&gt;""),Registro_Mensual!G4:G63),"")</f>
         <v>506</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="45"/>
+      <c r="E4" s="50"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
@@ -5627,10 +5627,10 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="48"/>
+      <c r="B10" s="45"/>
       <c r="D10" s="17" t="s">
         <v>33</v>
       </c>
@@ -5667,67 +5667,72 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="49" t="s">
+      <c r="D12" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="49"/>
+      <c r="E12" s="46"/>
     </row>
     <row r="13" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
     </row>
     <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
     </row>
     <row r="15" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
     </row>
     <row r="16" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+      <c r="A16" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
     </row>
     <row r="17" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="47" t="s">
+      <c r="A17" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="47"/>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
     </row>
     <row r="18" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
@@ -5736,11 +5741,6 @@
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C7" s="27">
         <f t="shared" si="1"/>
-        <v>367.14</v>
+        <v>407.14</v>
       </c>
       <c r="E7" t="s">
         <v>44</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Q9" s="39">
         <f t="shared" si="0"/>
-        <v>0.3238575725235277</v>
+        <v>0.30418274049998484</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
@@ -6042,22 +6042,22 @@
         <v>46261</v>
       </c>
       <c r="G10" s="32">
-        <v>337.61</v>
+        <v>377.61</v>
       </c>
       <c r="H10" s="32">
         <f>SUM($G$3:G10)</f>
-        <v>618.42000000000007</v>
+        <v>658.42000000000007</v>
       </c>
       <c r="O10" t="s">
         <v>62</v>
       </c>
       <c r="P10" s="40" cm="1">
         <f t="array" ref="P10">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O10)*$G$3:$G$104)</f>
-        <v>418.14</v>
+        <v>458.14</v>
       </c>
       <c r="Q10" s="39">
         <f t="shared" si="0"/>
-        <v>0.67614242747647235</v>
+        <v>0.69581725950001516</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="C12" s="38">
         <f>SUM(C3:C11)</f>
-        <v>618.41999999999996</v>
+        <v>658.42</v>
       </c>
       <c r="O12" t="s">
         <v>64</v>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="C13" s="33">
         <f>C12*0.19*-1</f>
-        <v>-117.49979999999999</v>
+        <v>-125.09979999999999</v>
       </c>
       <c r="O13" t="s">
         <v>65</v>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="C14" s="36">
         <f>C12+C13</f>
-        <v>500.92019999999997</v>
+        <v>533.3202</v>
       </c>
       <c r="O14" t="s">
         <v>66</v>

--- a/inversiones_2026.xlsx
+++ b/inversiones_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\Documents\GitHub\inversiones\inversiones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E6BCF5-8D27-41F1-85CC-C29606E5E96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B668A5F9-B133-4E9D-85CA-B0455544BC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,17 +17,15 @@
     <sheet name="Resumen" sheetId="2" r:id="rId2"/>
     <sheet name="Beneficios bolsa" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">'Beneficios bolsa'!$B$3:$B$11</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'Beneficios bolsa'!$C$2</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'Beneficios bolsa'!$C$3:$C$11</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Beneficios bolsa'!$D$2</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'Beneficios bolsa'!$D$3:$D$11</definedName>
+  </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -35,30 +33,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="73">
   <si>
     <t>📈 SEGUIMIENTO DE INVERSIONES — S&amp;P 500</t>
   </si>
@@ -276,6 +252,18 @@
   <si>
     <t>Nvidia</t>
   </si>
+  <si>
+    <t>Alphabet</t>
+  </si>
+  <si>
+    <t>Uber</t>
+  </si>
+  <si>
+    <t>SpaceX</t>
+  </si>
+  <si>
+    <t>Prop</t>
+  </si>
 </sst>
 </file>
 
@@ -405,7 +393,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -490,8 +478,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor rgb="FFEBF5FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -597,13 +591,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -689,10 +692,22 @@
     <xf numFmtId="166" fontId="0" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -708,17 +723,34 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -726,7 +758,26 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1005,7 +1056,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Beneficios bolsa'!$G$2</c:f>
+              <c:f>'Beneficios bolsa'!$H$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1026,9 +1077,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Beneficios bolsa'!$E$3:$F$10</c:f>
+              <c:f>'Beneficios bolsa'!$F$3:$G$15</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="13"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>15-jul</c:v>
@@ -1053,6 +1104,21 @@
                   </c:pt>
                   <c:pt idx="7">
                     <c:v>27-ago</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>28-ago</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>28-ago</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>28-ago</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>31-ago</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>02-sep</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1080,16 +1146,31 @@
                   <c:pt idx="7">
                     <c:v>Nvidia</c:v>
                   </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Alphabet</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Uber</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>SpaceX</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>SpaceX</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Uber</c:v>
+                  </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Beneficios bolsa'!$G$3:$G$10</c:f>
+              <c:f>'Beneficios bolsa'!$H$3:$H$15</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* "-"??\ [$€-C0A]_-;_-@_-</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1113,6 +1194,21 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>377.61</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>40.25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>66.930000000000007</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>124.16</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>39.39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1144,7 +1240,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Beneficios bolsa'!$H$2</c:f>
+              <c:f>'Beneficios bolsa'!$I$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1167,9 +1263,9 @@
           </c:marker>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Beneficios bolsa'!$E$3:$F$10</c:f>
+              <c:f>'Beneficios bolsa'!$F$3:$G$15</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="13"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>15-jul</c:v>
@@ -1194,6 +1290,21 @@
                   </c:pt>
                   <c:pt idx="7">
                     <c:v>27-ago</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>28-ago</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>28-ago</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>28-ago</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>31-ago</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>02-sep</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1221,16 +1332,31 @@
                   <c:pt idx="7">
                     <c:v>Nvidia</c:v>
                   </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Alphabet</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Uber</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>SpaceX</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>SpaceX</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Uber</c:v>
+                  </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Beneficios bolsa'!$H$3:$H$10</c:f>
+              <c:f>'Beneficios bolsa'!$I$3:$I$15</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* "-"??\ [$€-C0A]_-;_-@_-</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1254,6 +1380,21 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>658.42000000000007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>664.42000000000007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>704.67000000000007</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>771.60000000000014</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>895.7600000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>935.15000000000009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1288,7 +1429,7 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
+        <c:tickLblPos val="low"/>
         <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -1398,7 +1539,7 @@
         <c:crossAx val="1885366847"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="50"/>
+        <c:majorUnit val="200"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1532,7 +1673,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Beneficios bolsa'!$P$2</c:f>
+              <c:f>'Beneficios bolsa'!$Q$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1553,7 +1694,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Beneficios bolsa'!$O$3:$O$14</c:f>
+              <c:f>'Beneficios bolsa'!$P$3:$P$14</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -1597,7 +1738,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Beneficios bolsa'!$P$3:$P$14</c:f>
+              <c:f>'Beneficios bolsa'!$Q$3:$Q$14</c:f>
               <c:numCache>
                 <c:formatCode>_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1623,10 +1764,10 @@
                   <c:v>200.28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>458.14</c:v>
+                  <c:v>695.4799999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>39.39</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -1667,7 +1808,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Beneficios bolsa'!$Q$2</c:f>
+              <c:f>'Beneficios bolsa'!$R$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1690,7 +1831,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Beneficios bolsa'!$O$3:$O$14</c:f>
+              <c:f>'Beneficios bolsa'!$P$3:$P$14</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -1734,7 +1875,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Beneficios bolsa'!$Q$3:$Q$14</c:f>
+              <c:f>'Beneficios bolsa'!$R$3:$R$14</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1757,13 +1898,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.30418274049998484</c:v>
+                  <c:v>0.21416884991712562</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.69581725950001516</c:v>
+                  <c:v>0.74370956531037802</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>4.2121584772496397E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -2040,6 +2181,61 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="size">
+        <cx:f>_xlchart.v1.2</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="size">
+        <cx:f>_xlchart.v1.4</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="treemap" uniqueId="{7EA71D80-B4CB-41BB-B5A4-ACC62A489E92}" formatIdx="0">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:v> Balance </cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataLabels pos="inEnd">
+            <cx:visibility seriesName="0" categoryName="1" value="0"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:parentLabelLayout val="overlapping"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="treemap" hidden="1" uniqueId="{85EA78A7-92EB-4523-98B8-D779EEC2DD29}" formatIdx="1">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.3</cx:f>
+              <cx:v> Prop </cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr/>
+        </cx:series>
+      </cx:plotAreaRegion>
+    </cx:plotArea>
+    <cx:legend pos="t" align="ctr" overlay="0"/>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2120,6 +2316,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="225">
   <cs:axisTitle>
@@ -3123,17 +3359,539 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="410">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1">
+          <a:lumMod val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>42862</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>561975</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>119062</xdr:rowOff>
@@ -3163,13 +3921,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>312965</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>91167</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>557893</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>167367</xdr:rowOff>
@@ -3197,19 +3955,100 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>23132</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>367393</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>99332</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Gráfico 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D488503-7A7F-4DDF-8147-592693D90139}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11171464" y="2880632"/>
+              <a:ext cx="5687786" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-ES" sz="1100"/>
+                <a:t>Este gráfico no está disponible en su versión de Excel.
+Si edita esta forma o guarda el libro en un formato de archivo diferente, el gráfico no se podrá utilizar.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{43361EA0-38CE-405F-999E-E678479A76FE}" name="Tabla3" displayName="Tabla3" ref="B2:C11" totalsRowShown="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="B2:C11" xr:uid="{43361EA0-38CE-405F-999E-E678479A76FE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{43361EA0-38CE-405F-999E-E678479A76FE}" name="Tabla3" displayName="Tabla3" ref="B2:D11" totalsRowShown="0" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="B2:D11" xr:uid="{43361EA0-38CE-405F-999E-E678479A76FE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:C11">
     <sortCondition descending="1" ref="C3:C11"/>
   </sortState>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5452176F-36B8-4CDD-9F33-5D70AA66A550}" name="Mercado" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{AA88D4F0-70F9-4823-81E5-D366BE0621A3}" name="Balance" dataDxfId="5" dataCellStyle="Moneda">
-      <calculatedColumnFormula>SUMIF(E:E,B3,G:G)</calculatedColumnFormula>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{5452176F-36B8-4CDD-9F33-5D70AA66A550}" name="Mercado" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{AA88D4F0-70F9-4823-81E5-D366BE0621A3}" name="Balance" dataDxfId="6" dataCellStyle="Moneda">
+      <calculatedColumnFormula>SUMIF(F:F,B3,H:H)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{863A4A40-7E14-4485-AAD9-12FD76E33499}" name="Prop" dataDxfId="0" dataCellStyle="Porcentaje">
+      <calculatedColumnFormula>Tabla3[[#This Row],[Balance]]/$C$12</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3217,14 +4056,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}" name="Tabla4" displayName="Tabla4" ref="E2:H10" totalsRowShown="0">
-  <autoFilter ref="E2:H10" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}" name="Tabla4" displayName="Tabla4" ref="F2:I15" totalsRowShown="0">
+  <autoFilter ref="F2:I15" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{D7244F53-013B-49D1-84D7-0E66C32F39B4}" name="Mercado"/>
-    <tableColumn id="2" xr3:uid="{28786B65-FA4E-4DA6-9569-A775903889EB}" name="Fecha venta" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00894C4B-3E6A-4755-9F14-59B8AD97246A}" name="Balance" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{2A5F1324-D18F-4866-A09B-AC0F8A8E977C}" name="Acumulado" dataDxfId="2">
-      <calculatedColumnFormula>SUM($G$3:G3)</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{28786B65-FA4E-4DA6-9569-A775903889EB}" name="Fecha venta" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00894C4B-3E6A-4755-9F14-59B8AD97246A}" name="Balance" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{2A5F1324-D18F-4866-A09B-AC0F8A8E977C}" name="Acumulado" dataDxfId="3">
+      <calculatedColumnFormula>SUM($H$3:H3)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3232,15 +4071,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{85052AB3-E623-41D6-B93A-D236D62ED596}" name="Tabla1" displayName="Tabla1" ref="O2:Q14" totalsRowShown="0">
-  <autoFilter ref="O2:Q14" xr:uid="{85052AB3-E623-41D6-B93A-D236D62ED596}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{85052AB3-E623-41D6-B93A-D236D62ED596}" name="Tabla1" displayName="Tabla1" ref="P2:R14" totalsRowShown="0">
+  <autoFilter ref="P2:R14" xr:uid="{85052AB3-E623-41D6-B93A-D236D62ED596}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{21FC16B9-6E5E-4AAD-BCF0-C6A776FA39F3}" name="Mes"/>
-    <tableColumn id="2" xr3:uid="{37D9736B-4BBA-4113-BEB6-FB1048207595}" name="Balance" dataDxfId="1">
-      <calculatedColumnFormula array="1">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O3)*$G$3:$G$104)</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{37D9736B-4BBA-4113-BEB6-FB1048207595}" name="Balance" dataDxfId="2">
+      <calculatedColumnFormula array="1">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P3)*$H$3:$H$109)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5B181ADE-DC8F-4395-A0B1-0AC4441D7B3C}" name="Peso anual" dataDxfId="0" dataCellStyle="Porcentaje">
-      <calculatedColumnFormula>IFERROR($P3/SUM($P$3:$P$14),0)</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{5B181ADE-DC8F-4395-A0B1-0AC4441D7B3C}" name="Peso anual" dataDxfId="1" dataCellStyle="Porcentaje">
+      <calculatedColumnFormula>IFERROR($Q3/SUM($Q$3:$Q$14),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3438,30 +4277,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
+      <c r="A1" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -3694,31 +4533,37 @@
       <c r="A9" s="12">
         <v>6</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="6"/>
+      <c r="B9" s="5">
+        <v>46236</v>
+      </c>
+      <c r="C9" s="6">
+        <v>200</v>
+      </c>
       <c r="D9" s="7">
         <v>0</v>
       </c>
       <c r="E9" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="6"/>
+        <v>200</v>
+      </c>
+      <c r="F9" s="6">
+        <v>730</v>
+      </c>
       <c r="G9" s="14">
         <f>SUM($C$4:C9)</f>
-        <v>506</v>
-      </c>
-      <c r="H9" s="14" t="str">
+        <v>706</v>
+      </c>
+      <c r="H9" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I9" s="15" t="str">
+        <v>24</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3.3994334277620331E-2</v>
       </c>
       <c r="J9" s="14">
         <f>AVERAGE($E$4:E9)</f>
-        <v>82.833333333333329</v>
+        <v>116.16666666666667</v>
       </c>
       <c r="K9" s="11"/>
     </row>
@@ -3738,7 +4583,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="9">
         <f>SUM($C$4:C10)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H10" s="9" t="str">
         <f t="shared" si="1"/>
@@ -3750,7 +4595,7 @@
       </c>
       <c r="J10" s="9">
         <f>AVERAGE($E$4:E10)</f>
-        <v>71</v>
+        <v>99.571428571428569</v>
       </c>
       <c r="K10" s="11"/>
     </row>
@@ -3770,7 +4615,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="14">
         <f>SUM($C$4:C11)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H11" s="14" t="str">
         <f t="shared" si="1"/>
@@ -3782,7 +4627,7 @@
       </c>
       <c r="J11" s="14">
         <f>AVERAGE($E$4:E11)</f>
-        <v>62.125</v>
+        <v>87.125</v>
       </c>
       <c r="K11" s="11"/>
     </row>
@@ -3802,7 +4647,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="9">
         <f>SUM($C$4:C12)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H12" s="9" t="str">
         <f t="shared" si="1"/>
@@ -3814,7 +4659,7 @@
       </c>
       <c r="J12" s="9">
         <f>AVERAGE($E$4:E12)</f>
-        <v>55.222222222222221</v>
+        <v>77.444444444444443</v>
       </c>
       <c r="K12" s="11"/>
     </row>
@@ -3834,7 +4679,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="14">
         <f>SUM($C$4:C13)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H13" s="14" t="str">
         <f t="shared" si="1"/>
@@ -3846,7 +4691,7 @@
       </c>
       <c r="J13" s="14">
         <f>AVERAGE($E$4:E13)</f>
-        <v>49.7</v>
+        <v>69.7</v>
       </c>
       <c r="K13" s="11"/>
     </row>
@@ -3866,7 +4711,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="9">
         <f>SUM($C$4:C14)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H14" s="9" t="str">
         <f t="shared" si="1"/>
@@ -3878,41 +4723,41 @@
       </c>
       <c r="J14" s="9">
         <f>AVERAGE($E$4:E14)</f>
-        <v>45.18181818181818</v>
+        <v>63.363636363636367</v>
       </c>
       <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
+      <c r="A15" s="55">
         <v>12</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7">
-        <v>0</v>
-      </c>
-      <c r="E15" s="8">
+      <c r="B15" s="56"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="58">
+        <v>0</v>
+      </c>
+      <c r="E15" s="59">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="14">
+      <c r="F15" s="57"/>
+      <c r="G15" s="60">
         <f>SUM($C$4:C15)</f>
-        <v>506</v>
-      </c>
-      <c r="H15" s="14" t="str">
+        <v>706</v>
+      </c>
+      <c r="H15" s="60" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I15" s="15" t="str">
+      <c r="I15" s="61" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="60">
         <f>AVERAGE($E$4:E15)</f>
-        <v>41.416666666666664</v>
-      </c>
-      <c r="K15" s="11"/>
+        <v>58.083333333333336</v>
+      </c>
+      <c r="K15" s="62"/>
     </row>
     <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
@@ -3930,7 +4775,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="9">
         <f>SUM($C$4:C16)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H16" s="9" t="str">
         <f t="shared" si="1"/>
@@ -3942,7 +4787,7 @@
       </c>
       <c r="J16" s="9">
         <f>AVERAGE($E$4:E16)</f>
-        <v>38.230769230769234</v>
+        <v>53.615384615384613</v>
       </c>
       <c r="K16" s="11"/>
     </row>
@@ -3962,7 +4807,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="14">
         <f>SUM($C$4:C17)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H17" s="14" t="str">
         <f t="shared" si="1"/>
@@ -3974,7 +4819,7 @@
       </c>
       <c r="J17" s="14">
         <f>AVERAGE($E$4:E17)</f>
-        <v>35.5</v>
+        <v>49.785714285714285</v>
       </c>
       <c r="K17" s="11"/>
     </row>
@@ -3994,7 +4839,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="9">
         <f>SUM($C$4:C18)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H18" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4006,7 +4851,7 @@
       </c>
       <c r="J18" s="9">
         <f>AVERAGE($E$4:E18)</f>
-        <v>33.133333333333333</v>
+        <v>46.466666666666669</v>
       </c>
       <c r="K18" s="11"/>
     </row>
@@ -4026,7 +4871,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="14">
         <f>SUM($C$4:C19)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H19" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4038,7 +4883,7 @@
       </c>
       <c r="J19" s="14">
         <f>AVERAGE($E$4:E19)</f>
-        <v>31.0625</v>
+        <v>43.5625</v>
       </c>
       <c r="K19" s="11"/>
     </row>
@@ -4058,7 +4903,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="9">
         <f>SUM($C$4:C20)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H20" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4070,7 +4915,7 @@
       </c>
       <c r="J20" s="9">
         <f>AVERAGE($E$4:E20)</f>
-        <v>29.235294117647058</v>
+        <v>41</v>
       </c>
       <c r="K20" s="11"/>
     </row>
@@ -4090,7 +4935,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="14">
         <f>SUM($C$4:C21)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H21" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4102,7 +4947,7 @@
       </c>
       <c r="J21" s="14">
         <f>AVERAGE($E$4:E21)</f>
-        <v>27.611111111111111</v>
+        <v>38.722222222222221</v>
       </c>
       <c r="K21" s="11"/>
     </row>
@@ -4122,7 +4967,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="9">
         <f>SUM($C$4:C22)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H22" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4134,7 +4979,7 @@
       </c>
       <c r="J22" s="9">
         <f>AVERAGE($E$4:E22)</f>
-        <v>26.157894736842106</v>
+        <v>36.684210526315788</v>
       </c>
       <c r="K22" s="11"/>
     </row>
@@ -4154,7 +4999,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="14">
         <f>SUM($C$4:C23)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H23" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4166,7 +5011,7 @@
       </c>
       <c r="J23" s="14">
         <f>AVERAGE($E$4:E23)</f>
-        <v>24.85</v>
+        <v>34.85</v>
       </c>
       <c r="K23" s="11"/>
     </row>
@@ -4186,7 +5031,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="9">
         <f>SUM($C$4:C24)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H24" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4198,7 +5043,7 @@
       </c>
       <c r="J24" s="9">
         <f>AVERAGE($E$4:E24)</f>
-        <v>23.666666666666668</v>
+        <v>33.19047619047619</v>
       </c>
       <c r="K24" s="11"/>
     </row>
@@ -4218,7 +5063,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="14">
         <f>SUM($C$4:C25)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H25" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4230,7 +5075,7 @@
       </c>
       <c r="J25" s="14">
         <f>AVERAGE($E$4:E25)</f>
-        <v>22.59090909090909</v>
+        <v>31.681818181818183</v>
       </c>
       <c r="K25" s="11"/>
     </row>
@@ -4250,7 +5095,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="9">
         <f>SUM($C$4:C26)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H26" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4262,7 +5107,7 @@
       </c>
       <c r="J26" s="9">
         <f>AVERAGE($E$4:E26)</f>
-        <v>21.608695652173914</v>
+        <v>30.304347826086957</v>
       </c>
       <c r="K26" s="11"/>
     </row>
@@ -4282,7 +5127,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="14">
         <f>SUM($C$4:C27)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H27" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4294,7 +5139,7 @@
       </c>
       <c r="J27" s="14">
         <f>AVERAGE($E$4:E27)</f>
-        <v>20.708333333333332</v>
+        <v>29.041666666666668</v>
       </c>
       <c r="K27" s="11"/>
     </row>
@@ -4314,7 +5159,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="9">
         <f>SUM($C$4:C28)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H28" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4326,7 +5171,7 @@
       </c>
       <c r="J28" s="9">
         <f>AVERAGE($E$4:E28)</f>
-        <v>19.88</v>
+        <v>27.88</v>
       </c>
       <c r="K28" s="11"/>
     </row>
@@ -4346,7 +5191,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="14">
         <f>SUM($C$4:C29)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H29" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4358,7 +5203,7 @@
       </c>
       <c r="J29" s="14">
         <f>AVERAGE($E$4:E29)</f>
-        <v>19.115384615384617</v>
+        <v>26.807692307692307</v>
       </c>
       <c r="K29" s="11"/>
     </row>
@@ -4378,7 +5223,7 @@
       <c r="F30" s="6"/>
       <c r="G30" s="9">
         <f>SUM($C$4:C30)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H30" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4390,7 +5235,7 @@
       </c>
       <c r="J30" s="9">
         <f>AVERAGE($E$4:E30)</f>
-        <v>18.407407407407408</v>
+        <v>25.814814814814813</v>
       </c>
       <c r="K30" s="11"/>
     </row>
@@ -4410,7 +5255,7 @@
       <c r="F31" s="6"/>
       <c r="G31" s="14">
         <f>SUM($C$4:C31)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H31" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4422,7 +5267,7 @@
       </c>
       <c r="J31" s="14">
         <f>AVERAGE($E$4:E31)</f>
-        <v>17.75</v>
+        <v>24.892857142857142</v>
       </c>
       <c r="K31" s="11"/>
     </row>
@@ -4442,7 +5287,7 @@
       <c r="F32" s="6"/>
       <c r="G32" s="9">
         <f>SUM($C$4:C32)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H32" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4454,7 +5299,7 @@
       </c>
       <c r="J32" s="9">
         <f>AVERAGE($E$4:E32)</f>
-        <v>17.137931034482758</v>
+        <v>24.03448275862069</v>
       </c>
       <c r="K32" s="11"/>
     </row>
@@ -4474,7 +5319,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="14">
         <f>SUM($C$4:C33)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H33" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4486,7 +5331,7 @@
       </c>
       <c r="J33" s="14">
         <f>AVERAGE($E$4:E33)</f>
-        <v>16.566666666666666</v>
+        <v>23.233333333333334</v>
       </c>
       <c r="K33" s="11"/>
     </row>
@@ -4506,7 +5351,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="9">
         <f>SUM($C$4:C34)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H34" s="9" t="str">
         <f t="shared" si="1"/>
@@ -4518,7 +5363,7 @@
       </c>
       <c r="J34" s="9">
         <f>AVERAGE($E$4:E34)</f>
-        <v>16.032258064516128</v>
+        <v>22.483870967741936</v>
       </c>
       <c r="K34" s="11"/>
     </row>
@@ -4538,7 +5383,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="14">
         <f>SUM($C$4:C35)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H35" s="14" t="str">
         <f t="shared" si="1"/>
@@ -4550,7 +5395,7 @@
       </c>
       <c r="J35" s="14">
         <f>AVERAGE($E$4:E35)</f>
-        <v>15.53125</v>
+        <v>21.78125</v>
       </c>
       <c r="K35" s="11"/>
     </row>
@@ -4570,7 +5415,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="9">
         <f>SUM($C$4:C36)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H36" s="9" t="str">
         <f t="shared" ref="H36:H63" si="4">IF(F36="","",F36-G36)</f>
@@ -4582,7 +5427,7 @@
       </c>
       <c r="J36" s="9">
         <f>AVERAGE($E$4:E36)</f>
-        <v>15.060606060606061</v>
+        <v>21.121212121212121</v>
       </c>
       <c r="K36" s="11"/>
     </row>
@@ -4602,7 +5447,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="14">
         <f>SUM($C$4:C37)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H37" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4614,7 +5459,7 @@
       </c>
       <c r="J37" s="14">
         <f>AVERAGE($E$4:E37)</f>
-        <v>14.617647058823529</v>
+        <v>20.5</v>
       </c>
       <c r="K37" s="11"/>
     </row>
@@ -4634,7 +5479,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="9">
         <f>SUM($C$4:C38)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H38" s="9" t="str">
         <f t="shared" si="4"/>
@@ -4646,7 +5491,7 @@
       </c>
       <c r="J38" s="9">
         <f>AVERAGE($E$4:E38)</f>
-        <v>14.2</v>
+        <v>19.914285714285715</v>
       </c>
       <c r="K38" s="11"/>
     </row>
@@ -4666,7 +5511,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="14">
         <f>SUM($C$4:C39)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H39" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4678,7 +5523,7 @@
       </c>
       <c r="J39" s="14">
         <f>AVERAGE($E$4:E39)</f>
-        <v>13.805555555555555</v>
+        <v>19.361111111111111</v>
       </c>
       <c r="K39" s="11"/>
     </row>
@@ -4698,7 +5543,7 @@
       <c r="F40" s="6"/>
       <c r="G40" s="9">
         <f>SUM($C$4:C40)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H40" s="9" t="str">
         <f t="shared" si="4"/>
@@ -4710,7 +5555,7 @@
       </c>
       <c r="J40" s="9">
         <f>AVERAGE($E$4:E40)</f>
-        <v>13.432432432432432</v>
+        <v>18.837837837837839</v>
       </c>
       <c r="K40" s="11"/>
     </row>
@@ -4730,7 +5575,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="14">
         <f>SUM($C$4:C41)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H41" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4742,7 +5587,7 @@
       </c>
       <c r="J41" s="14">
         <f>AVERAGE($E$4:E41)</f>
-        <v>13.078947368421053</v>
+        <v>18.342105263157894</v>
       </c>
       <c r="K41" s="11"/>
     </row>
@@ -4762,7 +5607,7 @@
       <c r="F42" s="6"/>
       <c r="G42" s="9">
         <f>SUM($C$4:C42)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H42" s="9" t="str">
         <f t="shared" si="4"/>
@@ -4774,7 +5619,7 @@
       </c>
       <c r="J42" s="9">
         <f>AVERAGE($E$4:E42)</f>
-        <v>12.743589743589743</v>
+        <v>17.871794871794872</v>
       </c>
       <c r="K42" s="11"/>
     </row>
@@ -4794,7 +5639,7 @@
       <c r="F43" s="6"/>
       <c r="G43" s="14">
         <f>SUM($C$4:C43)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H43" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4806,7 +5651,7 @@
       </c>
       <c r="J43" s="14">
         <f>AVERAGE($E$4:E43)</f>
-        <v>12.425000000000001</v>
+        <v>17.425000000000001</v>
       </c>
       <c r="K43" s="11"/>
     </row>
@@ -4826,7 +5671,7 @@
       <c r="F44" s="6"/>
       <c r="G44" s="9">
         <f>SUM($C$4:C44)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H44" s="9" t="str">
         <f t="shared" si="4"/>
@@ -4838,7 +5683,7 @@
       </c>
       <c r="J44" s="9">
         <f>AVERAGE($E$4:E44)</f>
-        <v>12.121951219512194</v>
+        <v>17</v>
       </c>
       <c r="K44" s="11"/>
     </row>
@@ -4858,7 +5703,7 @@
       <c r="F45" s="6"/>
       <c r="G45" s="14">
         <f>SUM($C$4:C45)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H45" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4870,7 +5715,7 @@
       </c>
       <c r="J45" s="14">
         <f>AVERAGE($E$4:E45)</f>
-        <v>11.833333333333334</v>
+        <v>16.595238095238095</v>
       </c>
       <c r="K45" s="11"/>
     </row>
@@ -4890,7 +5735,7 @@
       <c r="F46" s="6"/>
       <c r="G46" s="9">
         <f>SUM($C$4:C46)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H46" s="9" t="str">
         <f t="shared" si="4"/>
@@ -4902,7 +5747,7 @@
       </c>
       <c r="J46" s="9">
         <f>AVERAGE($E$4:E46)</f>
-        <v>11.55813953488372</v>
+        <v>16.209302325581394</v>
       </c>
       <c r="K46" s="11"/>
     </row>
@@ -4922,7 +5767,7 @@
       <c r="F47" s="6"/>
       <c r="G47" s="14">
         <f>SUM($C$4:C47)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H47" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4934,7 +5779,7 @@
       </c>
       <c r="J47" s="14">
         <f>AVERAGE($E$4:E47)</f>
-        <v>11.295454545454545</v>
+        <v>15.840909090909092</v>
       </c>
       <c r="K47" s="11"/>
     </row>
@@ -4954,7 +5799,7 @@
       <c r="F48" s="6"/>
       <c r="G48" s="9">
         <f>SUM($C$4:C48)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H48" s="9" t="str">
         <f t="shared" si="4"/>
@@ -4966,7 +5811,7 @@
       </c>
       <c r="J48" s="9">
         <f>AVERAGE($E$4:E48)</f>
-        <v>11.044444444444444</v>
+        <v>15.488888888888889</v>
       </c>
       <c r="K48" s="11"/>
     </row>
@@ -4986,7 +5831,7 @@
       <c r="F49" s="6"/>
       <c r="G49" s="14">
         <f>SUM($C$4:C49)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H49" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4998,7 +5843,7 @@
       </c>
       <c r="J49" s="14">
         <f>AVERAGE($E$4:E49)</f>
-        <v>10.804347826086957</v>
+        <v>15.152173913043478</v>
       </c>
       <c r="K49" s="11"/>
     </row>
@@ -5018,7 +5863,7 @@
       <c r="F50" s="6"/>
       <c r="G50" s="9">
         <f>SUM($C$4:C50)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H50" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5030,7 +5875,7 @@
       </c>
       <c r="J50" s="9">
         <f>AVERAGE($E$4:E50)</f>
-        <v>10.574468085106384</v>
+        <v>14.829787234042554</v>
       </c>
       <c r="K50" s="11"/>
     </row>
@@ -5050,7 +5895,7 @@
       <c r="F51" s="6"/>
       <c r="G51" s="14">
         <f>SUM($C$4:C51)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H51" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5062,7 +5907,7 @@
       </c>
       <c r="J51" s="14">
         <f>AVERAGE($E$4:E51)</f>
-        <v>10.354166666666666</v>
+        <v>14.520833333333334</v>
       </c>
       <c r="K51" s="11"/>
     </row>
@@ -5082,7 +5927,7 @@
       <c r="F52" s="6"/>
       <c r="G52" s="9">
         <f>SUM($C$4:C52)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H52" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5094,7 +5939,7 @@
       </c>
       <c r="J52" s="9">
         <f>AVERAGE($E$4:E52)</f>
-        <v>10.142857142857142</v>
+        <v>14.224489795918368</v>
       </c>
       <c r="K52" s="11"/>
     </row>
@@ -5114,7 +5959,7 @@
       <c r="F53" s="6"/>
       <c r="G53" s="14">
         <f>SUM($C$4:C53)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H53" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5126,7 +5971,7 @@
       </c>
       <c r="J53" s="14">
         <f>AVERAGE($E$4:E53)</f>
-        <v>9.94</v>
+        <v>13.94</v>
       </c>
       <c r="K53" s="11"/>
     </row>
@@ -5146,7 +5991,7 @@
       <c r="F54" s="6"/>
       <c r="G54" s="9">
         <f>SUM($C$4:C54)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H54" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5158,7 +6003,7 @@
       </c>
       <c r="J54" s="9">
         <f>AVERAGE($E$4:E54)</f>
-        <v>9.7450980392156854</v>
+        <v>13.666666666666666</v>
       </c>
       <c r="K54" s="11"/>
     </row>
@@ -5178,7 +6023,7 @@
       <c r="F55" s="6"/>
       <c r="G55" s="14">
         <f>SUM($C$4:C55)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H55" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5190,7 +6035,7 @@
       </c>
       <c r="J55" s="14">
         <f>AVERAGE($E$4:E55)</f>
-        <v>9.5576923076923084</v>
+        <v>13.403846153846153</v>
       </c>
       <c r="K55" s="11"/>
     </row>
@@ -5210,7 +6055,7 @@
       <c r="F56" s="6"/>
       <c r="G56" s="9">
         <f>SUM($C$4:C56)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H56" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5222,7 +6067,7 @@
       </c>
       <c r="J56" s="9">
         <f>AVERAGE($E$4:E56)</f>
-        <v>9.3773584905660385</v>
+        <v>13.150943396226415</v>
       </c>
       <c r="K56" s="11"/>
     </row>
@@ -5242,7 +6087,7 @@
       <c r="F57" s="6"/>
       <c r="G57" s="14">
         <f>SUM($C$4:C57)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H57" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5254,7 +6099,7 @@
       </c>
       <c r="J57" s="14">
         <f>AVERAGE($E$4:E57)</f>
-        <v>9.2037037037037042</v>
+        <v>12.907407407407407</v>
       </c>
       <c r="K57" s="11"/>
     </row>
@@ -5274,7 +6119,7 @@
       <c r="F58" s="6"/>
       <c r="G58" s="9">
         <f>SUM($C$4:C58)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H58" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5286,7 +6131,7 @@
       </c>
       <c r="J58" s="9">
         <f>AVERAGE($E$4:E58)</f>
-        <v>9.036363636363637</v>
+        <v>12.672727272727272</v>
       </c>
       <c r="K58" s="11"/>
     </row>
@@ -5306,7 +6151,7 @@
       <c r="F59" s="6"/>
       <c r="G59" s="14">
         <f>SUM($C$4:C59)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H59" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5318,7 +6163,7 @@
       </c>
       <c r="J59" s="14">
         <f>AVERAGE($E$4:E59)</f>
-        <v>8.875</v>
+        <v>12.446428571428571</v>
       </c>
       <c r="K59" s="11"/>
     </row>
@@ -5338,7 +6183,7 @@
       <c r="F60" s="6"/>
       <c r="G60" s="9">
         <f>SUM($C$4:C60)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H60" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5350,7 +6195,7 @@
       </c>
       <c r="J60" s="9">
         <f>AVERAGE($E$4:E60)</f>
-        <v>8.7192982456140342</v>
+        <v>12.228070175438596</v>
       </c>
       <c r="K60" s="11"/>
     </row>
@@ -5370,7 +6215,7 @@
       <c r="F61" s="6"/>
       <c r="G61" s="14">
         <f>SUM($C$4:C61)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H61" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5382,7 +6227,7 @@
       </c>
       <c r="J61" s="14">
         <f>AVERAGE($E$4:E61)</f>
-        <v>8.568965517241379</v>
+        <v>12.017241379310345</v>
       </c>
       <c r="K61" s="11"/>
     </row>
@@ -5402,7 +6247,7 @@
       <c r="F62" s="6"/>
       <c r="G62" s="9">
         <f>SUM($C$4:C62)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H62" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5414,7 +6259,7 @@
       </c>
       <c r="J62" s="9">
         <f>AVERAGE($E$4:E62)</f>
-        <v>8.4237288135593218</v>
+        <v>11.813559322033898</v>
       </c>
       <c r="K62" s="11"/>
     </row>
@@ -5434,7 +6279,7 @@
       <c r="F63" s="6"/>
       <c r="G63" s="14">
         <f>SUM($C$4:C63)</f>
-        <v>506</v>
+        <v>706</v>
       </c>
       <c r="H63" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5446,7 +6291,7 @@
       </c>
       <c r="J63" s="14">
         <f>AVERAGE($E$4:E63)</f>
-        <v>8.2833333333333332</v>
+        <v>11.616666666666667</v>
       </c>
       <c r="K63" s="11"/>
     </row>
@@ -5473,32 +6318,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="D3" s="49" t="s">
+      <c r="B3" s="45"/>
+      <c r="D3" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="49"/>
+      <c r="E3" s="45"/>
       <c r="F3" s="16" t="s">
         <v>18</v>
       </c>
@@ -5512,12 +6357,12 @@
       </c>
       <c r="B4" s="18">
         <f>IFERROR(LOOKUP(2,1/(Registro_Mensual!G4:G63&lt;&gt;""),Registro_Mensual!G4:G63),"")</f>
-        <v>506</v>
-      </c>
-      <c r="D4" s="50" t="s">
+        <v>706</v>
+      </c>
+      <c r="D4" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="50"/>
+      <c r="E4" s="46"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
@@ -5525,14 +6370,14 @@
       </c>
       <c r="B5" s="18">
         <f ca="1">OFFSET(Registro_Mensual!F3,COUNTA(Registro_Mensual!F4:F63),0)</f>
-        <v>525</v>
+        <v>730</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="18">
         <f>B8</f>
-        <v>99.4</v>
+        <v>116.16666666666667</v>
       </c>
       <c r="F5" s="19"/>
       <c r="G5" s="19"/>
@@ -5543,7 +6388,7 @@
       </c>
       <c r="B6" s="18">
         <f ca="1">IFERROR(B5-B4,"")</f>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>25</v>
@@ -5560,22 +6405,22 @@
       </c>
       <c r="B7" s="21">
         <f ca="1">IFERROR(B5/B4-1,"")</f>
-        <v>3.7549407114624511E-2</v>
+        <v>3.3994334277620331E-2</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="18">
         <f>E5*((1+E6/12)^60-1)/(E6/12)</f>
-        <v>7116.3344238223854</v>
+        <v>8316.7087414557391</v>
       </c>
       <c r="F7" s="23">
         <f>E5*60</f>
-        <v>5964</v>
+        <v>6970</v>
       </c>
       <c r="G7" s="23">
         <f>E7-F7</f>
-        <v>1152.3344238223854</v>
+        <v>1346.7087414557391</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5584,22 +6429,22 @@
       </c>
       <c r="B8" s="18">
         <f>IFERROR(AVERAGEIF(Registro_Mensual!C4:C63,"&gt;0",Registro_Mensual!E4:E63),"")</f>
-        <v>99.4</v>
+        <v>116.16666666666667</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E8" s="18">
         <f>E5*((1+E6/12)^120-1)/(E6/12)</f>
-        <v>17204.629858893561</v>
+        <v>20106.685130195863</v>
       </c>
       <c r="F8" s="23">
         <f>E5*120</f>
-        <v>11928</v>
+        <v>13940</v>
       </c>
       <c r="G8" s="23">
         <f>E8-F8</f>
-        <v>5276.6298588935606</v>
+        <v>6166.6851301958632</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5608,43 +6453,43 @@
       </c>
       <c r="B9" s="22">
         <f>COUNTIF(Registro_Mensual!C4:C63,"&gt;0")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="18">
         <f>E5*((1+E6/12)^240-1)/(E6/12)</f>
-        <v>51780.109986656382</v>
+        <v>60514.313649730873</v>
       </c>
       <c r="F9" s="23">
         <f>E5*240</f>
-        <v>23856</v>
+        <v>27880</v>
       </c>
       <c r="G9" s="23">
         <f>E9-F9</f>
-        <v>27924.109986656382</v>
+        <v>32634.313649730873</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="45"/>
+      <c r="B10" s="49"/>
       <c r="D10" s="17" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="18">
         <f>E5*((1+E6/12)^360-1)/(E6/12)</f>
-        <v>121265.11698012863</v>
+        <v>141719.96400930526</v>
       </c>
       <c r="F10" s="23">
         <f>E5*360</f>
-        <v>35784</v>
+        <v>41820</v>
       </c>
       <c r="G10" s="23">
         <f>E10-F10</f>
-        <v>85481.116980128631</v>
+        <v>99899.964009305259</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5655,84 +6500,79 @@
       </c>
       <c r="E11" s="18">
         <f>E5*((1+E6/12)^480-1)/(E6/12)</f>
-        <v>260906.45179433568</v>
+        <v>304915.82310639165</v>
       </c>
       <c r="F11" s="23">
         <f>E5*480</f>
-        <v>47712</v>
+        <v>55760</v>
       </c>
       <c r="G11" s="23">
         <f>E11-F11</f>
-        <v>213194.45179433568</v>
+        <v>249155.82310639165</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="46"/>
+      <c r="E12" s="50"/>
     </row>
     <row r="13" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
     </row>
     <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
     </row>
     <row r="15" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
     </row>
     <row r="16" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
     </row>
     <row r="17" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
     </row>
     <row r="18" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
@@ -5741,6 +6581,11 @@
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5749,403 +6594,522 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6C2CF63-A9CC-4BE2-B119-A050F91FC767}">
-  <dimension ref="B1:Q14"/>
+  <dimension ref="B1:R15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" style="25" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="32"/>
-    <col min="16" max="16" width="11.42578125" style="40"/>
-    <col min="17" max="17" width="12.7109375" style="39" customWidth="1"/>
+    <col min="3" max="4" width="13.42578125" style="25" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" style="32"/>
+    <col min="17" max="17" width="11.42578125" style="40"/>
+    <col min="18" max="18" width="12.7109375" style="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="51" t="s">
+    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="E1" s="51" t="s">
+      <c r="C1" s="52"/>
+      <c r="D1" s="41"/>
+      <c r="F1" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-    </row>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+    </row>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B2" s="30" t="s">
         <v>46</v>
       </c>
       <c r="C2" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
         <v>46</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="H2" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>53</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="40" t="s">
+      <c r="Q2" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="Q2" s="39" t="s">
+      <c r="R2" s="39" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B3" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C3" s="27">
-        <f>SUMIF(E:E,B3,G:G)</f>
+        <f>SUMIF(F:F,B3,H:H)</f>
         <v>131</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D3" s="54">
+        <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
+        <v>0.14008447842592098</v>
+      </c>
+      <c r="F3" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="24">
+      <c r="G3" s="24">
         <v>46218</v>
       </c>
-      <c r="G3" s="32">
+      <c r="H3" s="32">
         <v>8</v>
       </c>
-      <c r="H3" s="32">
-        <f>SUM($G$3:G3)</f>
+      <c r="I3" s="32">
+        <f>SUM($H$3:H3)</f>
         <v>8</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="40" cm="1">
-        <f t="array" ref="P3">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O3)*$G$3:$G$104)</f>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="39">
-        <f t="shared" ref="Q3:Q14" si="0">IFERROR($P3/SUM($P$3:$P$14),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q3" s="40">
+        <f t="array" ref="Q3">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P3)*$H$3:$H$109)</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="39">
+        <f t="shared" ref="R3:R14" si="0">IFERROR($Q3/SUM($Q$3:$Q$14),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B4" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="27">
-        <f t="shared" ref="C4:C11" si="1">SUMIF(E:E,B4,G:G)</f>
+        <f>SUMIF(F:F,B4,H:H)</f>
         <v>53.4</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" s="54">
+        <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
+        <v>5.7103138533925041E-2</v>
+      </c>
+      <c r="F4" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="24">
+      <c r="G4" s="24">
         <v>46219</v>
       </c>
-      <c r="G4" s="32">
+      <c r="H4" s="32">
         <v>7.88</v>
       </c>
-      <c r="H4" s="32">
-        <f>SUM($G$3:G4)</f>
+      <c r="I4" s="32">
+        <f>SUM($H$3:H4)</f>
         <v>15.879999999999999</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>56</v>
       </c>
-      <c r="P4" s="40" cm="1">
-        <f t="array" ref="P4">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O4)*$G$3:$G$104)</f>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="40">
+        <f t="array" ref="Q4">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P4)*$H$3:$H$109)</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C5" s="27">
-        <f t="shared" si="1"/>
+        <f>SUMIF(F:F,B5,H:H)</f>
         <v>15.879999999999999</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D5" s="54">
+        <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
+        <v>1.6981232957279581E-2</v>
+      </c>
+      <c r="F5" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="24">
+      <c r="G5" s="24">
         <v>46220</v>
       </c>
-      <c r="G5" s="32">
+      <c r="H5" s="32">
         <v>19.399999999999999</v>
       </c>
-      <c r="H5" s="32">
-        <f>SUM($G$3:G5)</f>
+      <c r="I5" s="32">
+        <f>SUM($H$3:H5)</f>
         <v>35.28</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>57</v>
       </c>
-      <c r="P5" s="40" cm="1">
-        <f t="array" ref="P5">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O5)*$G$3:$G$104)</f>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="39">
+      <c r="Q5" s="40">
+        <f t="array" ref="Q5">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P5)*$H$3:$H$109)</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B6" s="26" t="s">
         <v>67</v>
       </c>
       <c r="C6" s="27">
-        <f t="shared" si="1"/>
+        <f>SUMIF(F:F,B6,H:H)</f>
         <v>51</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D6" s="54">
+        <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
+        <v>5.4536705341389081E-2</v>
+      </c>
+      <c r="F6" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="24">
+      <c r="G6" s="24">
         <v>46232</v>
       </c>
-      <c r="G6" s="32">
+      <c r="H6" s="32">
         <v>131</v>
       </c>
-      <c r="H6" s="32">
-        <f>SUM($G$3:G6)</f>
+      <c r="I6" s="32">
+        <f>SUM($H$3:H6)</f>
         <v>166.28</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>58</v>
       </c>
-      <c r="P6" s="40" cm="1">
-        <f t="array" ref="P6">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O6)*$G$3:$G$104)</f>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="39">
+      <c r="Q6" s="40">
+        <f t="array" ref="Q6">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P6)*$H$3:$H$109)</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="26" t="s">
         <v>68</v>
       </c>
       <c r="C7" s="27">
-        <f t="shared" si="1"/>
+        <f>SUMIF(F:F,B7,H:H)</f>
         <v>407.14</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D7" s="54">
+        <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
+        <v>0.43537400417045391</v>
+      </c>
+      <c r="F7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="24">
+      <c r="G7" s="24">
         <v>46234</v>
       </c>
-      <c r="G7" s="32">
+      <c r="H7" s="32">
         <v>34</v>
       </c>
-      <c r="H7" s="32">
-        <f>SUM($G$3:G7)</f>
+      <c r="I7" s="32">
+        <f>SUM($H$3:H7)</f>
         <v>200.28</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>59</v>
       </c>
-      <c r="P7" s="40" cm="1">
-        <f t="array" ref="P7">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O7)*$G$3:$G$104)</f>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="39">
+      <c r="Q7" s="40">
+        <f t="array" ref="Q7">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P7)*$H$3:$H$109)</f>
+        <v>0</v>
+      </c>
+      <c r="R7" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="26"/>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B8" s="26" t="s">
+        <v>69</v>
+      </c>
       <c r="C8" s="27">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E8" t="s">
+        <f>SUMIF(F:F,B8,H:H)</f>
+        <v>6</v>
+      </c>
+      <c r="D8" s="54">
+        <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
+        <v>6.4160829813398922E-3</v>
+      </c>
+      <c r="F8" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="24">
+      <c r="G8" s="24">
         <v>46254</v>
       </c>
-      <c r="G8" s="32">
+      <c r="H8" s="32">
         <v>51</v>
       </c>
-      <c r="H8" s="32">
-        <f>SUM($G$3:G8)</f>
+      <c r="I8" s="32">
+        <f>SUM($H$3:H8)</f>
         <v>251.28</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>60</v>
       </c>
-      <c r="P8" s="40" cm="1">
-        <f t="array" ref="P8">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O8)*$G$3:$G$104)</f>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="39">
+      <c r="Q8" s="40">
+        <f t="array" ref="Q8">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P8)*$H$3:$H$109)</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="26"/>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B9" s="26" t="s">
+        <v>70</v>
+      </c>
       <c r="C9" s="27">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E9" t="s">
+        <f>SUMIF(F:F,B9,H:H)</f>
+        <v>79.64</v>
+      </c>
+      <c r="D9" s="54">
+        <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
+        <v>8.5162808105651508E-2</v>
+      </c>
+      <c r="F9" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="24">
+      <c r="G9" s="24">
         <v>46260</v>
       </c>
-      <c r="G9" s="32">
+      <c r="H9" s="32">
         <v>29.53</v>
       </c>
-      <c r="H9" s="32">
-        <f>SUM($G$3:G9)</f>
+      <c r="I9" s="32">
+        <f>SUM($H$3:H9)</f>
         <v>280.81</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>61</v>
       </c>
-      <c r="P9" s="40" cm="1">
-        <f t="array" ref="P9">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O9)*$G$3:$G$104)</f>
+      <c r="Q9" s="40">
+        <f t="array" ref="Q9">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P9)*$H$3:$H$109)</f>
         <v>200.28</v>
       </c>
-      <c r="Q9" s="39">
+      <c r="R9" s="39">
         <f t="shared" si="0"/>
-        <v>0.30418274049998484</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="26"/>
+        <v>0.21416884991712562</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B10" s="26" t="s">
+        <v>71</v>
+      </c>
       <c r="C10" s="27">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E10" t="s">
+        <f>SUMIF(F:F,B10,H:H)</f>
+        <v>191.09</v>
+      </c>
+      <c r="D10" s="54">
+        <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
+        <v>0.20434154948404001</v>
+      </c>
+      <c r="F10" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="24">
+      <c r="G10" s="24">
         <v>46261</v>
       </c>
-      <c r="G10" s="32">
+      <c r="H10" s="32">
         <v>377.61</v>
       </c>
-      <c r="H10" s="32">
-        <f>SUM($G$3:G10)</f>
+      <c r="I10" s="32">
+        <f>SUM($H$3:H10)</f>
         <v>658.42000000000007</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>62</v>
       </c>
-      <c r="P10" s="40" cm="1">
-        <f t="array" ref="P10">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O10)*$G$3:$G$104)</f>
-        <v>458.14</v>
-      </c>
-      <c r="Q10" s="39">
+      <c r="Q10" s="40">
+        <f t="array" ref="Q10">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P10)*$H$3:$H$109)</f>
+        <v>695.4799999999999</v>
+      </c>
+      <c r="R10" s="39">
         <f t="shared" si="0"/>
-        <v>0.69581725950001516</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+        <v>0.74370956531037802</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="28"/>
       <c r="C11" s="29">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
+        <f>SUMIF(F:F,B11,H:H)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="54">
+        <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="24">
+        <v>46262</v>
+      </c>
+      <c r="H11" s="32">
+        <v>6</v>
+      </c>
+      <c r="I11" s="32">
+        <f>SUM($H$3:H11)</f>
+        <v>664.42000000000007</v>
+      </c>
+      <c r="P11" t="s">
         <v>63</v>
       </c>
-      <c r="P11" s="40" cm="1">
-        <f t="array" ref="P11">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O11)*$G$3:$G$104)</f>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="39">
+      <c r="Q11" s="40">
+        <f t="array" ref="Q11">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P11)*$H$3:$H$109)</f>
+        <v>39.39</v>
+      </c>
+      <c r="R11" s="39">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+        <v>4.2121584772496397E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="37" t="s">
         <v>43</v>
       </c>
       <c r="C12" s="38">
         <f>SUM(C3:C11)</f>
-        <v>658.42</v>
-      </c>
-      <c r="O12" t="s">
+        <v>935.15</v>
+      </c>
+      <c r="D12"/>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="24">
+        <v>46262</v>
+      </c>
+      <c r="H12" s="32">
+        <v>40.25</v>
+      </c>
+      <c r="I12" s="32">
+        <f>SUM($H$3:H12)</f>
+        <v>704.67000000000007</v>
+      </c>
+      <c r="P12" t="s">
         <v>64</v>
       </c>
-      <c r="P12" s="40" cm="1">
-        <f t="array" ref="P12">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O12)*$G$3:$G$104)</f>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="39">
+      <c r="Q12" s="40">
+        <f t="array" ref="Q12">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P12)*$H$3:$H$109)</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
         <v>51</v>
       </c>
       <c r="C13" s="33">
         <f>C12*0.19*-1</f>
-        <v>-125.09979999999999</v>
-      </c>
-      <c r="O13" t="s">
+        <v>-177.67849999999999</v>
+      </c>
+      <c r="D13"/>
+      <c r="F13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="24">
+        <v>46262</v>
+      </c>
+      <c r="H13" s="32">
+        <f>43.58+23.35</f>
+        <v>66.930000000000007</v>
+      </c>
+      <c r="I13" s="32">
+        <f>SUM($H$3:H13)</f>
+        <v>771.60000000000014</v>
+      </c>
+      <c r="P13" t="s">
         <v>65</v>
       </c>
-      <c r="P13" s="40" cm="1">
-        <f t="array" ref="P13">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O13)*$G$3:$G$104)</f>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="39">
+      <c r="Q13" s="40">
+        <f t="array" ref="Q13">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P13)*$H$3:$H$109)</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="35" t="s">
         <v>52</v>
       </c>
       <c r="C14" s="36">
         <f>C12+C13</f>
-        <v>533.3202</v>
-      </c>
-      <c r="O14" t="s">
+        <v>757.47149999999999</v>
+      </c>
+      <c r="D14"/>
+      <c r="F14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="24">
+        <v>46265</v>
+      </c>
+      <c r="H14" s="32">
+        <f>47.38+80.22-3.44</f>
+        <v>124.16</v>
+      </c>
+      <c r="I14" s="32">
+        <f>SUM($H$3:H14)</f>
+        <v>895.7600000000001</v>
+      </c>
+      <c r="P14" t="s">
         <v>66</v>
       </c>
-      <c r="P14" s="40" cm="1">
-        <f t="array" ref="P14">SUMPRODUCT(($F$3:$F$104&lt;&gt;"")*(TEXT($F$3:$F$104,"mmmm")=O14)*$G$3:$G$104)</f>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="39">
+      <c r="Q14" s="40">
+        <f t="array" ref="Q14">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P14)*$H$3:$H$109)</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="D15"/>
+      <c r="F15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="24">
+        <v>46267</v>
+      </c>
+      <c r="H15" s="32">
+        <v>39.39</v>
+      </c>
+      <c r="I15" s="32">
+        <f>SUM($H$3:H15)</f>
+        <v>935.15000000000009</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="F1:I1"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
-  <conditionalFormatting sqref="C3:C11">
-    <cfRule type="dataBar" priority="4">
+  <conditionalFormatting sqref="C3:D11">
+    <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6158,8 +7122,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C15:C1048576 C3:C11">
-    <cfRule type="dataBar" priority="3">
+  <conditionalFormatting sqref="C16:D1048576 C15 C3:D11">
+    <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6172,8 +7136,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
-    <cfRule type="dataBar" priority="2">
+  <conditionalFormatting sqref="C2:D2">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6186,8 +7150,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
-    <cfRule type="dataBar" priority="1">
+  <conditionalFormatting sqref="C2:D2">
+    <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6198,6 +7162,16 @@
           <x14:id>{A19D6E6F-6841-43C9-8235-0F835BE2EFF0}</x14:id>
         </ext>
       </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:D11">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6221,7 +7195,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>C3:C11</xm:sqref>
+          <xm:sqref>C3:D11</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{77F84ACE-D316-480D-B918-04CEA84DBCE9}">
@@ -6234,7 +7208,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>C15:C1048576 C3:C11</xm:sqref>
+          <xm:sqref>C16:D1048576 C15 C3:D11</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{8574F4BE-9390-4DEC-A36D-A8EC7E2D95CF}">
@@ -6247,7 +7221,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>C2</xm:sqref>
+          <xm:sqref>C2:D2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{A19D6E6F-6841-43C9-8235-0F835BE2EFF0}">
@@ -6260,7 +7234,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>C2</xm:sqref>
+          <xm:sqref>C2:D2</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/inversiones_2026.xlsx
+++ b/inversiones_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\Documents\GitHub\inversiones\inversiones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B668A5F9-B133-4E9D-85CA-B0455544BC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18D393B-86D7-42FB-A5E3-D0A890A805D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro_Mensual" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="74">
   <si>
     <t>📈 SEGUIMIENTO DE INVERSIONES — S&amp;P 500</t>
   </si>
@@ -264,6 +264,9 @@
   <si>
     <t>Prop</t>
   </si>
+  <si>
+    <t>CoreWeave</t>
+  </si>
 </sst>
 </file>
 
@@ -485,7 +488,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -570,17 +573,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -606,7 +598,7 @@
     <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -677,8 +669,7 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -695,38 +686,7 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -752,6 +712,37 @@
     <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -759,25 +750,6 @@
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="11">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -809,6 +781,25 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="21" formatCode="dd\-mmm"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1077,9 +1068,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Beneficios bolsa'!$F$3:$G$15</c:f>
+              <c:f>'Beneficios bolsa'!$F$3:$G$17</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="15"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>15-jul</c:v>
@@ -1119,6 +1110,12 @@
                   </c:pt>
                   <c:pt idx="12">
                     <c:v>02-sep</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>03-sep</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>04-sep</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1161,16 +1158,22 @@
                   <c:pt idx="12">
                     <c:v>Uber</c:v>
                   </c:pt>
+                  <c:pt idx="13">
+                    <c:v>SpaceX</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>CoreWeave</c:v>
+                  </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Beneficios bolsa'!$H$3:$H$15</c:f>
+              <c:f>'Beneficios bolsa'!$H$3:$H$17</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* "-"??\ [$€-C0A]_-;_-@_-</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1208,7 +1211,13 @@
                   <c:v>124.16</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>39.39</c:v>
+                  <c:v>4.3900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>319.77</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>28.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1263,9 +1272,9 @@
           </c:marker>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Beneficios bolsa'!$F$3:$G$15</c:f>
+              <c:f>'Beneficios bolsa'!$F$3:$G$17</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="15"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>15-jul</c:v>
@@ -1305,6 +1314,12 @@
                   </c:pt>
                   <c:pt idx="12">
                     <c:v>02-sep</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>03-sep</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>04-sep</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1347,16 +1362,22 @@
                   <c:pt idx="12">
                     <c:v>Uber</c:v>
                   </c:pt>
+                  <c:pt idx="13">
+                    <c:v>SpaceX</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>CoreWeave</c:v>
+                  </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Beneficios bolsa'!$I$3:$I$15</c:f>
+              <c:f>'Beneficios bolsa'!$I$3:$I$17</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* "-"??\ [$€-C0A]_-;_-@_-</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1394,7 +1415,13 @@
                   <c:v>895.7600000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>935.15000000000009</c:v>
+                  <c:v>900.15000000000009</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1219.92</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1248.42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1767,7 +1794,7 @@
                   <c:v>695.4799999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>39.39</c:v>
+                  <c:v>352.65999999999997</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -1898,13 +1925,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.21416884991712562</c:v>
+                  <c:v>0.16042677944922384</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.74370956531037802</c:v>
+                  <c:v>0.55708815943352397</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.2121584772496397E-2</c:v>
+                  <c:v>0.28248506111725219</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -4002,8 +4029,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11171464" y="2880632"/>
-              <a:ext cx="5687786" cy="2743200"/>
+              <a:off x="12068175" y="2880632"/>
+              <a:ext cx="5691868" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4047,7 +4074,7 @@
     <tableColumn id="3" xr3:uid="{AA88D4F0-70F9-4823-81E5-D366BE0621A3}" name="Balance" dataDxfId="6" dataCellStyle="Moneda">
       <calculatedColumnFormula>SUMIF(F:F,B3,H:H)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{863A4A40-7E14-4485-AAD9-12FD76E33499}" name="Prop" dataDxfId="0" dataCellStyle="Porcentaje">
+    <tableColumn id="2" xr3:uid="{863A4A40-7E14-4485-AAD9-12FD76E33499}" name="Prop" dataDxfId="5" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>Tabla3[[#This Row],[Balance]]/$C$12</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4056,13 +4083,13 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}" name="Tabla4" displayName="Tabla4" ref="F2:I15" totalsRowShown="0">
-  <autoFilter ref="F2:I15" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}" name="Tabla4" displayName="Tabla4" ref="F2:I17" totalsRowShown="0">
+  <autoFilter ref="F2:I17" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{D7244F53-013B-49D1-84D7-0E66C32F39B4}" name="Mercado"/>
-    <tableColumn id="2" xr3:uid="{28786B65-FA4E-4DA6-9569-A775903889EB}" name="Fecha venta" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{00894C4B-3E6A-4755-9F14-59B8AD97246A}" name="Balance" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{2A5F1324-D18F-4866-A09B-AC0F8A8E977C}" name="Acumulado" dataDxfId="3">
+    <tableColumn id="2" xr3:uid="{28786B65-FA4E-4DA6-9569-A775903889EB}" name="Fecha venta" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00894C4B-3E6A-4755-9F14-59B8AD97246A}" name="Balance" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{2A5F1324-D18F-4866-A09B-AC0F8A8E977C}" name="Acumulado" dataDxfId="2">
       <calculatedColumnFormula>SUM($H$3:H3)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4075,10 +4102,10 @@
   <autoFilter ref="P2:R14" xr:uid="{85052AB3-E623-41D6-B93A-D236D62ED596}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{21FC16B9-6E5E-4AAD-BCF0-C6A776FA39F3}" name="Mes"/>
-    <tableColumn id="2" xr3:uid="{37D9736B-4BBA-4113-BEB6-FB1048207595}" name="Balance" dataDxfId="2">
-      <calculatedColumnFormula array="1">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P3)*$H$3:$H$109)</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{37D9736B-4BBA-4113-BEB6-FB1048207595}" name="Balance" dataDxfId="1">
+      <calculatedColumnFormula array="1">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P3)*$H$3:$H$111)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5B181ADE-DC8F-4395-A0B1-0AC4441D7B3C}" name="Peso anual" dataDxfId="1" dataCellStyle="Porcentaje">
+    <tableColumn id="3" xr3:uid="{5B181ADE-DC8F-4395-A0B1-0AC4441D7B3C}" name="Peso anual" dataDxfId="0" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IFERROR($Q3/SUM($Q$3:$Q$14),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4269,7 +4296,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -4277,30 +4304,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -4728,36 +4755,36 @@
       <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="55">
+      <c r="A15" s="43">
         <v>12</v>
       </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="58">
-        <v>0</v>
-      </c>
-      <c r="E15" s="59">
+      <c r="B15" s="44"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="46">
+        <v>0</v>
+      </c>
+      <c r="E15" s="47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15" s="57"/>
-      <c r="G15" s="60">
+      <c r="F15" s="45"/>
+      <c r="G15" s="48">
         <f>SUM($C$4:C15)</f>
         <v>706</v>
       </c>
-      <c r="H15" s="60" t="str">
+      <c r="H15" s="48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I15" s="61" t="str">
+      <c r="I15" s="49" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J15" s="60">
+      <c r="J15" s="48">
         <f>AVERAGE($E$4:E15)</f>
         <v>58.083333333333336</v>
       </c>
-      <c r="K15" s="62"/>
+      <c r="K15" s="50"/>
     </row>
     <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
@@ -6318,32 +6345,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="D3" s="45" t="s">
+      <c r="B3" s="59"/>
+      <c r="D3" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="45"/>
+      <c r="E3" s="59"/>
       <c r="F3" s="16" t="s">
         <v>18</v>
       </c>
@@ -6359,10 +6386,10 @@
         <f>IFERROR(LOOKUP(2,1/(Registro_Mensual!G4:G63&lt;&gt;""),Registro_Mensual!G4:G63),"")</f>
         <v>706</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="46"/>
+      <c r="E4" s="60"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
@@ -6472,10 +6499,10 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="49"/>
+      <c r="B10" s="55"/>
       <c r="D10" s="17" t="s">
         <v>33</v>
       </c>
@@ -6512,67 +6539,72 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="50" t="s">
+      <c r="D12" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="50"/>
+      <c r="E12" s="56"/>
     </row>
     <row r="13" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="51"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
     </row>
     <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
     </row>
     <row r="15" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
     </row>
     <row r="16" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="47" t="s">
+      <c r="A16" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
     </row>
     <row r="17" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
     </row>
     <row r="18" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
@@ -6581,11 +6613,6 @@
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6594,39 +6621,39 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6C2CF63-A9CC-4BE2-B119-A050F91FC767}">
-  <dimension ref="B1:R15"/>
+  <dimension ref="B1:R17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="4" width="13.42578125" style="25" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="32"/>
-    <col min="17" max="17" width="11.42578125" style="40"/>
-    <col min="18" max="18" width="12.7109375" style="39" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" style="31"/>
+    <col min="17" max="17" width="11.42578125" style="39"/>
+    <col min="18" max="18" width="12.7109375" style="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="41"/>
-      <c r="F1" s="52" t="s">
+      <c r="C1" s="61"/>
+      <c r="D1" s="40"/>
+      <c r="F1" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="41" t="s">
         <v>72</v>
       </c>
       <c r="F2" t="s">
@@ -6635,7 +6662,7 @@
       <c r="G2" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="31" t="s">
         <v>48</v>
       </c>
       <c r="I2" t="s">
@@ -6644,10 +6671,10 @@
       <c r="P2" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="40" t="s">
+      <c r="Q2" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="R2" s="39" t="s">
+      <c r="R2" s="38" t="s">
         <v>54</v>
       </c>
     </row>
@@ -6656,12 +6683,12 @@
         <v>42</v>
       </c>
       <c r="C3" s="27">
-        <f>SUMIF(F:F,B3,H:H)</f>
+        <f t="shared" ref="C3:C11" si="0">SUMIF(F:F,B3,H:H)</f>
         <v>131</v>
       </c>
-      <c r="D3" s="54">
+      <c r="D3" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>0.14008447842592098</v>
+        <v>0.10493263485045097</v>
       </c>
       <c r="F3" t="s">
         <v>45</v>
@@ -6669,22 +6696,22 @@
       <c r="G3" s="24">
         <v>46218</v>
       </c>
-      <c r="H3" s="32">
+      <c r="H3" s="31">
         <v>8</v>
       </c>
-      <c r="I3" s="32">
+      <c r="I3" s="31">
         <f>SUM($H$3:H3)</f>
         <v>8</v>
       </c>
       <c r="P3" t="s">
         <v>55</v>
       </c>
-      <c r="Q3" s="40">
-        <f t="array" ref="Q3">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P3)*$H$3:$H$109)</f>
-        <v>0</v>
-      </c>
-      <c r="R3" s="39">
-        <f t="shared" ref="R3:R14" si="0">IFERROR($Q3/SUM($Q$3:$Q$14),0)</f>
+      <c r="Q3" s="39">
+        <f t="array" ref="Q3">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P3)*$H$3:$H$111)</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="38">
+        <f t="shared" ref="R3:R14" si="1">IFERROR($Q3/SUM($Q$3:$Q$14),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6693,12 +6720,12 @@
         <v>44</v>
       </c>
       <c r="C4" s="27">
-        <f>SUMIF(F:F,B4,H:H)</f>
+        <f t="shared" si="0"/>
         <v>53.4</v>
       </c>
-      <c r="D4" s="54">
+      <c r="D4" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>5.7103138533925041E-2</v>
+        <v>4.277406641995482E-2</v>
       </c>
       <c r="F4" t="s">
         <v>45</v>
@@ -6706,22 +6733,22 @@
       <c r="G4" s="24">
         <v>46219</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="31">
         <v>7.88</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="31">
         <f>SUM($H$3:H4)</f>
         <v>15.879999999999999</v>
       </c>
       <c r="P4" t="s">
         <v>56</v>
       </c>
-      <c r="Q4" s="40">
-        <f t="array" ref="Q4">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P4)*$H$3:$H$109)</f>
-        <v>0</v>
-      </c>
-      <c r="R4" s="39">
-        <f t="shared" si="0"/>
+      <c r="Q4" s="39">
+        <f t="array" ref="Q4">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P4)*$H$3:$H$111)</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="38">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -6730,12 +6757,12 @@
         <v>45</v>
       </c>
       <c r="C5" s="27">
-        <f>SUMIF(F:F,B5,H:H)</f>
+        <f t="shared" si="0"/>
         <v>15.879999999999999</v>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>1.6981232957279581E-2</v>
+        <v>1.2720078178818024E-2</v>
       </c>
       <c r="F5" t="s">
         <v>44</v>
@@ -6743,22 +6770,22 @@
       <c r="G5" s="24">
         <v>46220</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="31">
         <v>19.399999999999999</v>
       </c>
-      <c r="I5" s="32">
+      <c r="I5" s="31">
         <f>SUM($H$3:H5)</f>
         <v>35.28</v>
       </c>
       <c r="P5" t="s">
         <v>57</v>
       </c>
-      <c r="Q5" s="40">
-        <f t="array" ref="Q5">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P5)*$H$3:$H$109)</f>
-        <v>0</v>
-      </c>
-      <c r="R5" s="39">
-        <f t="shared" si="0"/>
+      <c r="Q5" s="39">
+        <f t="array" ref="Q5">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P5)*$H$3:$H$111)</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="38">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -6767,12 +6794,12 @@
         <v>67</v>
       </c>
       <c r="C6" s="27">
-        <f>SUMIF(F:F,B6,H:H)</f>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>5.4536705341389081E-2</v>
+        <v>4.0851636468496176E-2</v>
       </c>
       <c r="F6" t="s">
         <v>42</v>
@@ -6780,22 +6807,22 @@
       <c r="G6" s="24">
         <v>46232</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="31">
         <v>131</v>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="31">
         <f>SUM($H$3:H6)</f>
         <v>166.28</v>
       </c>
       <c r="P6" t="s">
         <v>58</v>
       </c>
-      <c r="Q6" s="40">
-        <f t="array" ref="Q6">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P6)*$H$3:$H$109)</f>
-        <v>0</v>
-      </c>
-      <c r="R6" s="39">
-        <f t="shared" si="0"/>
+      <c r="Q6" s="39">
+        <f t="array" ref="Q6">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P6)*$H$3:$H$111)</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="38">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -6804,12 +6831,12 @@
         <v>68</v>
       </c>
       <c r="C7" s="27">
-        <f>SUMIF(F:F,B7,H:H)</f>
+        <f t="shared" si="0"/>
         <v>407.14</v>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>0.43537400417045391</v>
+        <v>0.32612422101536337</v>
       </c>
       <c r="F7" t="s">
         <v>44</v>
@@ -6817,22 +6844,22 @@
       <c r="G7" s="24">
         <v>46234</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="31">
         <v>34</v>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="31">
         <f>SUM($H$3:H7)</f>
         <v>200.28</v>
       </c>
       <c r="P7" t="s">
         <v>59</v>
       </c>
-      <c r="Q7" s="40">
-        <f t="array" ref="Q7">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P7)*$H$3:$H$109)</f>
-        <v>0</v>
-      </c>
-      <c r="R7" s="39">
-        <f t="shared" si="0"/>
+      <c r="Q7" s="39">
+        <f t="array" ref="Q7">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P7)*$H$3:$H$111)</f>
+        <v>0</v>
+      </c>
+      <c r="R7" s="38">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -6841,12 +6868,12 @@
         <v>69</v>
       </c>
       <c r="C8" s="27">
-        <f>SUMIF(F:F,B8,H:H)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>6.4160829813398922E-3</v>
+        <v>4.8060748786466091E-3</v>
       </c>
       <c r="F8" t="s">
         <v>67</v>
@@ -6854,22 +6881,22 @@
       <c r="G8" s="24">
         <v>46254</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="31">
         <v>51</v>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="31">
         <f>SUM($H$3:H8)</f>
         <v>251.28</v>
       </c>
       <c r="P8" t="s">
         <v>60</v>
       </c>
-      <c r="Q8" s="40">
-        <f t="array" ref="Q8">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P8)*$H$3:$H$109)</f>
-        <v>0</v>
-      </c>
-      <c r="R8" s="39">
-        <f t="shared" si="0"/>
+      <c r="Q8" s="39">
+        <f t="array" ref="Q8">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P8)*$H$3:$H$111)</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="38">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -6878,12 +6905,12 @@
         <v>70</v>
       </c>
       <c r="C9" s="27">
-        <f>SUMIF(F:F,B9,H:H)</f>
-        <v>79.64</v>
-      </c>
-      <c r="D9" s="54">
+        <f t="shared" si="0"/>
+        <v>44.64</v>
+      </c>
+      <c r="D9" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>8.5162808105651508E-2</v>
+        <v>3.5757197097130773E-2</v>
       </c>
       <c r="F9" t="s">
         <v>68</v>
@@ -6891,23 +6918,23 @@
       <c r="G9" s="24">
         <v>46260</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="31">
         <v>29.53</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="31">
         <f>SUM($H$3:H9)</f>
         <v>280.81</v>
       </c>
       <c r="P9" t="s">
         <v>61</v>
       </c>
-      <c r="Q9" s="40">
-        <f t="array" ref="Q9">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P9)*$H$3:$H$109)</f>
+      <c r="Q9" s="39">
+        <f t="array" ref="Q9">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P9)*$H$3:$H$111)</f>
         <v>200.28</v>
       </c>
-      <c r="R9" s="39">
-        <f t="shared" si="0"/>
-        <v>0.21416884991712562</v>
+      <c r="R9" s="38">
+        <f t="shared" si="1"/>
+        <v>0.16042677944922384</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
@@ -6915,12 +6942,12 @@
         <v>71</v>
       </c>
       <c r="C10" s="27">
-        <f>SUMIF(F:F,B10,H:H)</f>
-        <v>191.09</v>
-      </c>
-      <c r="D10" s="54">
+        <f t="shared" si="0"/>
+        <v>510.86</v>
+      </c>
+      <c r="D10" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>0.20434154948404001</v>
+        <v>0.40920523541756781</v>
       </c>
       <c r="F10" t="s">
         <v>68</v>
@@ -6928,34 +6955,36 @@
       <c r="G10" s="24">
         <v>46261</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="31">
         <v>377.61</v>
       </c>
-      <c r="I10" s="32">
+      <c r="I10" s="31">
         <f>SUM($H$3:H10)</f>
         <v>658.42000000000007</v>
       </c>
       <c r="P10" t="s">
         <v>62</v>
       </c>
-      <c r="Q10" s="40">
-        <f t="array" ref="Q10">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P10)*$H$3:$H$109)</f>
+      <c r="Q10" s="39">
+        <f t="array" ref="Q10">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P10)*$H$3:$H$111)</f>
         <v>695.4799999999999</v>
       </c>
-      <c r="R10" s="39">
+      <c r="R10" s="38">
+        <f t="shared" si="1"/>
+        <v>0.55708815943352397</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="28">
         <f t="shared" si="0"/>
-        <v>0.74370956531037802</v>
-      </c>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="28"/>
-      <c r="C11" s="29">
-        <f>SUMIF(F:F,B11,H:H)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="54">
+        <v>28.5</v>
+      </c>
+      <c r="D11" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>0</v>
+        <v>2.2828855673571392E-2</v>
       </c>
       <c r="F11" t="s">
         <v>69</v>
@@ -6963,32 +6992,32 @@
       <c r="G11" s="24">
         <v>46262</v>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="31">
         <v>6</v>
       </c>
-      <c r="I11" s="32">
+      <c r="I11" s="31">
         <f>SUM($H$3:H11)</f>
         <v>664.42000000000007</v>
       </c>
       <c r="P11" t="s">
         <v>63</v>
       </c>
-      <c r="Q11" s="40">
-        <f t="array" ref="Q11">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P11)*$H$3:$H$109)</f>
-        <v>39.39</v>
-      </c>
-      <c r="R11" s="39">
-        <f t="shared" si="0"/>
-        <v>4.2121584772496397E-2</v>
+      <c r="Q11" s="39">
+        <f t="array" ref="Q11">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P11)*$H$3:$H$111)</f>
+        <v>352.65999999999997</v>
+      </c>
+      <c r="R11" s="38">
+        <f t="shared" si="1"/>
+        <v>0.28248506111725219</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="37">
         <f>SUM(C3:C11)</f>
-        <v>935.15</v>
+        <v>1248.42</v>
       </c>
       <c r="D12"/>
       <c r="F12" t="s">
@@ -6997,32 +7026,32 @@
       <c r="G12" s="24">
         <v>46262</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="31">
         <v>40.25</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="31">
         <f>SUM($H$3:H12)</f>
         <v>704.67000000000007</v>
       </c>
       <c r="P12" t="s">
         <v>64</v>
       </c>
-      <c r="Q12" s="40">
-        <f t="array" ref="Q12">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P12)*$H$3:$H$109)</f>
-        <v>0</v>
-      </c>
-      <c r="R12" s="39">
-        <f t="shared" si="0"/>
+      <c r="Q12" s="39">
+        <f t="array" ref="Q12">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P12)*$H$3:$H$111)</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="38">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="32">
         <f>C12*0.19*-1</f>
-        <v>-177.67849999999999</v>
+        <v>-237.19980000000001</v>
       </c>
       <c r="D13"/>
       <c r="F13" t="s">
@@ -7031,33 +7060,33 @@
       <c r="G13" s="24">
         <v>46262</v>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="31">
         <f>43.58+23.35</f>
         <v>66.930000000000007</v>
       </c>
-      <c r="I13" s="32">
+      <c r="I13" s="31">
         <f>SUM($H$3:H13)</f>
         <v>771.60000000000014</v>
       </c>
       <c r="P13" t="s">
         <v>65</v>
       </c>
-      <c r="Q13" s="40">
-        <f t="array" ref="Q13">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P13)*$H$3:$H$109)</f>
-        <v>0</v>
-      </c>
-      <c r="R13" s="39">
-        <f t="shared" si="0"/>
+      <c r="Q13" s="39">
+        <f t="array" ref="Q13">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P13)*$H$3:$H$111)</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="38">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="35">
         <f>C12+C13</f>
-        <v>757.47149999999999</v>
+        <v>1011.2202000000001</v>
       </c>
       <c r="D14"/>
       <c r="F14" t="s">
@@ -7066,23 +7095,23 @@
       <c r="G14" s="24">
         <v>46265</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="31">
         <f>47.38+80.22-3.44</f>
         <v>124.16</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="31">
         <f>SUM($H$3:H14)</f>
         <v>895.7600000000001</v>
       </c>
       <c r="P14" t="s">
         <v>66</v>
       </c>
-      <c r="Q14" s="40">
-        <f t="array" ref="Q14">SUMPRODUCT(($G$3:$G$109&lt;&gt;"")*(TEXT($G$3:$G$109,"mmmm")=P14)*$H$3:$H$109)</f>
-        <v>0</v>
-      </c>
-      <c r="R14" s="39">
-        <f t="shared" si="0"/>
+      <c r="Q14" s="39">
+        <f t="array" ref="Q14">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P14)*$H$3:$H$111)</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="38">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7094,12 +7123,45 @@
       <c r="G15" s="24">
         <v>46267</v>
       </c>
-      <c r="H15" s="32">
-        <v>39.39</v>
-      </c>
-      <c r="I15" s="32">
+      <c r="H15" s="31">
+        <f>39.39-35</f>
+        <v>4.3900000000000006</v>
+      </c>
+      <c r="I15" s="31">
         <f>SUM($H$3:H15)</f>
-        <v>935.15000000000009</v>
+        <v>900.15000000000009</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="24">
+        <v>46268</v>
+      </c>
+      <c r="H16" s="31">
+        <f>29.34+22.92+29.92+45.89+191.7</f>
+        <v>319.77</v>
+      </c>
+      <c r="I16" s="31">
+        <f>SUM($H$3:H16)</f>
+        <v>1219.92</v>
+      </c>
+    </row>
+    <row r="17" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="24">
+        <v>46269</v>
+      </c>
+      <c r="H17" s="31">
+        <f>113-84.5</f>
+        <v>28.5</v>
+      </c>
+      <c r="I17" s="31">
+        <f>SUM($H$3:H17)</f>
+        <v>1248.42</v>
       </c>
     </row>
   </sheetData>

--- a/inversiones_2026.xlsx
+++ b/inversiones_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\Documents\GitHub\inversiones\inversiones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18D393B-86D7-42FB-A5E3-D0A890A805D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB83182A-60ED-4E97-9241-60CD8A0B9A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,6 +25,7 @@
     <definedName name="_xlchart.v1.4" hidden="1">'Beneficios bolsa'!$D$3:$D$11</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="74">
   <si>
     <t>📈 SEGUIMIENTO DE INVERSIONES — S&amp;P 500</t>
   </si>
@@ -1068,9 +1069,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Beneficios bolsa'!$F$3:$G$17</c:f>
+              <c:f>'Beneficios bolsa'!$F$3:$G$18</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>15-jul</c:v>
@@ -1116,6 +1117,9 @@
                   </c:pt>
                   <c:pt idx="14">
                     <c:v>04-sep</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>22-sep</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1164,16 +1168,19 @@
                   <c:pt idx="14">
                     <c:v>CoreWeave</c:v>
                   </c:pt>
+                  <c:pt idx="15">
+                    <c:v>Nvidia</c:v>
+                  </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Beneficios bolsa'!$H$3:$H$17</c:f>
+              <c:f>'Beneficios bolsa'!$H$3:$H$18</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* "-"??\ [$€-C0A]_-;_-@_-</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1218,6 +1225,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>52</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1272,9 +1282,9 @@
           </c:marker>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Beneficios bolsa'!$F$3:$G$17</c:f>
+              <c:f>'Beneficios bolsa'!$F$3:$G$18</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>15-jul</c:v>
@@ -1320,6 +1330,9 @@
                   </c:pt>
                   <c:pt idx="14">
                     <c:v>04-sep</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>22-sep</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1368,16 +1381,19 @@
                   <c:pt idx="14">
                     <c:v>CoreWeave</c:v>
                   </c:pt>
+                  <c:pt idx="15">
+                    <c:v>Nvidia</c:v>
+                  </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Beneficios bolsa'!$I$3:$I$17</c:f>
+              <c:f>'Beneficios bolsa'!$I$3:$I$18</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* "-"??\ [$€-C0A]_-;_-@_-</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1422,6 +1438,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>1248.42</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1300.42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1794,7 +1813,7 @@
                   <c:v>695.4799999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>352.65999999999997</c:v>
+                  <c:v>404.65999999999997</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -1925,13 +1944,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.16042677944922384</c:v>
+                  <c:v>0.15401178080927702</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.55708815943352397</c:v>
+                  <c:v>0.53481183002414601</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.28248506111725219</c:v>
+                  <c:v>0.31117638916657697</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -4083,8 +4102,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}" name="Tabla4" displayName="Tabla4" ref="F2:I17" totalsRowShown="0">
-  <autoFilter ref="F2:I17" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}" name="Tabla4" displayName="Tabla4" ref="F2:I18" totalsRowShown="0">
+  <autoFilter ref="F2:I18" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{D7244F53-013B-49D1-84D7-0E66C32F39B4}" name="Mercado"/>
     <tableColumn id="2" xr3:uid="{28786B65-FA4E-4DA6-9569-A775903889EB}" name="Fecha venta" dataDxfId="4"/>
@@ -4103,7 +4122,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{21FC16B9-6E5E-4AAD-BCF0-C6A776FA39F3}" name="Mes"/>
     <tableColumn id="2" xr3:uid="{37D9736B-4BBA-4113-BEB6-FB1048207595}" name="Balance" dataDxfId="1">
-      <calculatedColumnFormula array="1">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P3)*$H$3:$H$111)</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">SUMPRODUCT(($G$3:$G$112&lt;&gt;"")*(TEXT($G$3:$G$112,"mmmm")=P3)*$H$3:$H$112)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{5B181ADE-DC8F-4395-A0B1-0AC4441D7B3C}" name="Peso anual" dataDxfId="0" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IFERROR($Q3/SUM($Q$3:$Q$14),0)</calculatedColumnFormula>
@@ -6621,7 +6640,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6C2CF63-A9CC-4BE2-B119-A050F91FC767}">
-  <dimension ref="B1:R17"/>
+  <dimension ref="B1:R18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -6688,7 +6707,7 @@
       </c>
       <c r="D3" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>0.10493263485045097</v>
+        <v>0.10073668507097706</v>
       </c>
       <c r="F3" t="s">
         <v>45</v>
@@ -6707,7 +6726,7 @@
         <v>55</v>
       </c>
       <c r="Q3" s="39">
-        <f t="array" ref="Q3">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P3)*$H$3:$H$111)</f>
+        <f t="array" ref="Q3">SUMPRODUCT(($G$3:$G$112&lt;&gt;"")*(TEXT($G$3:$G$112,"mmmm")=P3)*$H$3:$H$112)</f>
         <v>0</v>
       </c>
       <c r="R3" s="38">
@@ -6725,7 +6744,7 @@
       </c>
       <c r="D4" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>4.277406641995482E-2</v>
+        <v>4.106365635717691E-2</v>
       </c>
       <c r="F4" t="s">
         <v>45</v>
@@ -6744,7 +6763,7 @@
         <v>56</v>
       </c>
       <c r="Q4" s="39">
-        <f t="array" ref="Q4">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P4)*$H$3:$H$111)</f>
+        <f t="array" ref="Q4">SUMPRODUCT(($G$3:$G$112&lt;&gt;"")*(TEXT($G$3:$G$112,"mmmm")=P4)*$H$3:$H$112)</f>
         <v>0</v>
       </c>
       <c r="R4" s="38">
@@ -6762,7 +6781,7 @@
       </c>
       <c r="D5" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>1.2720078178818024E-2</v>
+        <v>1.221143938112302E-2</v>
       </c>
       <c r="F5" t="s">
         <v>44</v>
@@ -6781,7 +6800,7 @@
         <v>57</v>
       </c>
       <c r="Q5" s="39">
-        <f t="array" ref="Q5">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P5)*$H$3:$H$111)</f>
+        <f t="array" ref="Q5">SUMPRODUCT(($G$3:$G$112&lt;&gt;"")*(TEXT($G$3:$G$112,"mmmm")=P5)*$H$3:$H$112)</f>
         <v>0</v>
       </c>
       <c r="R5" s="38">
@@ -6799,7 +6818,7 @@
       </c>
       <c r="D6" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>4.0851636468496176E-2</v>
+        <v>3.9218098768090306E-2</v>
       </c>
       <c r="F6" t="s">
         <v>42</v>
@@ -6818,7 +6837,7 @@
         <v>58</v>
       </c>
       <c r="Q6" s="39">
-        <f t="array" ref="Q6">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P6)*$H$3:$H$111)</f>
+        <f t="array" ref="Q6">SUMPRODUCT(($G$3:$G$112&lt;&gt;"")*(TEXT($G$3:$G$112,"mmmm")=P6)*$H$3:$H$112)</f>
         <v>0</v>
       </c>
       <c r="R6" s="38">
@@ -6832,11 +6851,11 @@
       </c>
       <c r="C7" s="27">
         <f t="shared" si="0"/>
-        <v>407.14</v>
+        <v>459.14</v>
       </c>
       <c r="D7" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>0.32612422101536337</v>
+        <v>0.35307054643884278</v>
       </c>
       <c r="F7" t="s">
         <v>44</v>
@@ -6855,7 +6874,7 @@
         <v>59</v>
       </c>
       <c r="Q7" s="39">
-        <f t="array" ref="Q7">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P7)*$H$3:$H$111)</f>
+        <f t="array" ref="Q7">SUMPRODUCT(($G$3:$G$112&lt;&gt;"")*(TEXT($G$3:$G$112,"mmmm")=P7)*$H$3:$H$112)</f>
         <v>0</v>
       </c>
       <c r="R7" s="38">
@@ -6873,7 +6892,7 @@
       </c>
       <c r="D8" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>4.8060748786466091E-3</v>
+        <v>4.6138939727165063E-3</v>
       </c>
       <c r="F8" t="s">
         <v>67</v>
@@ -6892,7 +6911,7 @@
         <v>60</v>
       </c>
       <c r="Q8" s="39">
-        <f t="array" ref="Q8">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P8)*$H$3:$H$111)</f>
+        <f t="array" ref="Q8">SUMPRODUCT(($G$3:$G$112&lt;&gt;"")*(TEXT($G$3:$G$112,"mmmm")=P8)*$H$3:$H$112)</f>
         <v>0</v>
       </c>
       <c r="R8" s="38">
@@ -6910,7 +6929,7 @@
       </c>
       <c r="D9" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>3.5757197097130773E-2</v>
+        <v>3.4327371157010809E-2</v>
       </c>
       <c r="F9" t="s">
         <v>68</v>
@@ -6929,12 +6948,12 @@
         <v>61</v>
       </c>
       <c r="Q9" s="39">
-        <f t="array" ref="Q9">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P9)*$H$3:$H$111)</f>
+        <f t="array" ref="Q9">SUMPRODUCT(($G$3:$G$112&lt;&gt;"")*(TEXT($G$3:$G$112,"mmmm")=P9)*$H$3:$H$112)</f>
         <v>200.28</v>
       </c>
       <c r="R9" s="38">
         <f t="shared" si="1"/>
-        <v>0.16042677944922384</v>
+        <v>0.15401178080927702</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
@@ -6947,7 +6966,7 @@
       </c>
       <c r="D10" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>0.40920523541756781</v>
+        <v>0.39284231248365914</v>
       </c>
       <c r="F10" t="s">
         <v>68</v>
@@ -6966,12 +6985,12 @@
         <v>62</v>
       </c>
       <c r="Q10" s="39">
-        <f t="array" ref="Q10">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P10)*$H$3:$H$111)</f>
+        <f t="array" ref="Q10">SUMPRODUCT(($G$3:$G$112&lt;&gt;"")*(TEXT($G$3:$G$112,"mmmm")=P10)*$H$3:$H$112)</f>
         <v>695.4799999999999</v>
       </c>
       <c r="R10" s="38">
         <f t="shared" si="1"/>
-        <v>0.55708815943352397</v>
+        <v>0.53481183002414601</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
@@ -6984,7 +7003,7 @@
       </c>
       <c r="D11" s="42">
         <f>Tabla3[[#This Row],[Balance]]/$C$12</f>
-        <v>2.2828855673571392E-2</v>
+        <v>2.1915996370403406E-2</v>
       </c>
       <c r="F11" t="s">
         <v>69</v>
@@ -7003,12 +7022,12 @@
         <v>63</v>
       </c>
       <c r="Q11" s="39">
-        <f t="array" ref="Q11">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P11)*$H$3:$H$111)</f>
-        <v>352.65999999999997</v>
+        <f t="array" ref="Q11">SUMPRODUCT(($G$3:$G$112&lt;&gt;"")*(TEXT($G$3:$G$112,"mmmm")=P11)*$H$3:$H$112)</f>
+        <v>404.65999999999997</v>
       </c>
       <c r="R11" s="38">
         <f t="shared" si="1"/>
-        <v>0.28248506111725219</v>
+        <v>0.31117638916657697</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
@@ -7017,7 +7036,7 @@
       </c>
       <c r="C12" s="37">
         <f>SUM(C3:C11)</f>
-        <v>1248.42</v>
+        <v>1300.42</v>
       </c>
       <c r="D12"/>
       <c r="F12" t="s">
@@ -7037,7 +7056,7 @@
         <v>64</v>
       </c>
       <c r="Q12" s="39">
-        <f t="array" ref="Q12">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P12)*$H$3:$H$111)</f>
+        <f t="array" ref="Q12">SUMPRODUCT(($G$3:$G$112&lt;&gt;"")*(TEXT($G$3:$G$112,"mmmm")=P12)*$H$3:$H$112)</f>
         <v>0</v>
       </c>
       <c r="R12" s="38">
@@ -7051,7 +7070,7 @@
       </c>
       <c r="C13" s="32">
         <f>C12*0.19*-1</f>
-        <v>-237.19980000000001</v>
+        <v>-247.07980000000001</v>
       </c>
       <c r="D13"/>
       <c r="F13" t="s">
@@ -7072,7 +7091,7 @@
         <v>65</v>
       </c>
       <c r="Q13" s="39">
-        <f t="array" ref="Q13">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P13)*$H$3:$H$111)</f>
+        <f t="array" ref="Q13">SUMPRODUCT(($G$3:$G$112&lt;&gt;"")*(TEXT($G$3:$G$112,"mmmm")=P13)*$H$3:$H$112)</f>
         <v>0</v>
       </c>
       <c r="R13" s="38">
@@ -7086,7 +7105,7 @@
       </c>
       <c r="C14" s="35">
         <f>C12+C13</f>
-        <v>1011.2202000000001</v>
+        <v>1053.3402000000001</v>
       </c>
       <c r="D14"/>
       <c r="F14" t="s">
@@ -7107,7 +7126,7 @@
         <v>66</v>
       </c>
       <c r="Q14" s="39">
-        <f t="array" ref="Q14">SUMPRODUCT(($G$3:$G$111&lt;&gt;"")*(TEXT($G$3:$G$111,"mmmm")=P14)*$H$3:$H$111)</f>
+        <f t="array" ref="Q14">SUMPRODUCT(($G$3:$G$112&lt;&gt;"")*(TEXT($G$3:$G$112,"mmmm")=P14)*$H$3:$H$112)</f>
         <v>0</v>
       </c>
       <c r="R14" s="38">
@@ -7162,6 +7181,22 @@
       <c r="I17" s="31">
         <f>SUM($H$3:H17)</f>
         <v>1248.42</v>
+      </c>
+    </row>
+    <row r="18" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="24">
+        <v>46287</v>
+      </c>
+      <c r="H18" s="31">
+        <f>150-98</f>
+        <v>52</v>
+      </c>
+      <c r="I18" s="31">
+        <f>SUM($H$3:H18)</f>
+        <v>1300.42</v>
       </c>
     </row>
   </sheetData>
